--- a/YRIGOYEN 9730/Agosto/YRIGOYEN7630-Agosto.xlsx
+++ b/YRIGOYEN 9730/Agosto/YRIGOYEN7630-Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9730\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\YRIGOYEN 9730\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A26252F8-FB5D-40E8-9058-CEC754FB1CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866069E8-1B42-435A-9C3C-E702A9128657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -329,18 +329,6 @@
     <t>AGREGAR A LA CADENA</t>
   </si>
   <si>
-    <t>VTO 14/08</t>
-  </si>
-  <si>
-    <t>PERÍODO: JULIO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de JULIO</t>
-  </si>
-  <si>
-    <t>Ascensores lema - Mantenimiento junio</t>
-  </si>
-  <si>
     <t>Transf 17/7</t>
   </si>
   <si>
@@ -350,9 +338,6 @@
     <t>Transf 10/07</t>
   </si>
   <si>
-    <t>Julio Doartero - Cambio de caño cloacal UF 14</t>
-  </si>
-  <si>
     <t>Debito 14/07</t>
   </si>
   <si>
@@ -362,18 +347,12 @@
     <t>Efectivo 07/07</t>
   </si>
   <si>
-    <t>Debito 10/07</t>
-  </si>
-  <si>
     <t>Matafuegos - Recarga anual</t>
   </si>
   <si>
     <t>Debito 16/07</t>
   </si>
   <si>
-    <t>Julio Doartero - Visita inspeccion hidraulica</t>
-  </si>
-  <si>
     <t>Transf 25/07</t>
   </si>
   <si>
@@ -392,10 +371,31 @@
     <t>Mantenimiento de cuenta</t>
   </si>
   <si>
-    <t>Gustavo padron - Sr contador honorarios Junio y Julio</t>
-  </si>
-  <si>
     <t>Honorarios administracion</t>
+  </si>
+  <si>
+    <t>VTO 15/09</t>
+  </si>
+  <si>
+    <t>Debito 12/08</t>
+  </si>
+  <si>
+    <t>PERÍODO: AGOSTO</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de AGOSTO</t>
+  </si>
+  <si>
+    <t>AGOSTO Doartero - Visita inspeccion hidraulica</t>
+  </si>
+  <si>
+    <t>AGOSTO Doartero - Cambio de caño cloacal UF 14</t>
+  </si>
+  <si>
+    <t>Gustavo padron - Sr contador honorarios JULIO y AGOSTO</t>
+  </si>
+  <si>
+    <t>Ascensores lema - Mantenimiento JULIO</t>
   </si>
 </sst>
 </file>
@@ -403,14 +403,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="29" x14ac:knownFonts="1">
     <font>
@@ -1109,11 +1109,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1121,7 +1121,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1136,9 +1136,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1153,7 +1153,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1163,40 +1163,40 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1210,7 +1210,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1218,99 +1218,99 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="11" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1319,73 +1319,76 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="25" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="25" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="26" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="26" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1827,21 +1830,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M132"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="15"/>
       <c r="B1" s="71" t="s">
         <v>60</v>
@@ -1850,7 +1853,7 @@
       <c r="D1" s="71"/>
       <c r="E1" s="72"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="73" t="s">
         <v>29</v>
@@ -1859,16 +1862,16 @@
       <c r="D2" s="73"/>
       <c r="E2" s="74"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
-      <c r="B3" s="196" t="s">
+      <c r="B3" s="199" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="197"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="200"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
@@ -1879,12 +1882,12 @@
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>62</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="73" t="s">
@@ -1892,7 +1895,7 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>61</v>
       </c>
@@ -1903,57 +1906,57 @@
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="199" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="199"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="199"/>
-      <c r="C9" s="199"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="199"/>
-      <c r="C10" s="199"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="198" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="202" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="202"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="202"/>
+      <c r="C9" s="202"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="202"/>
+      <c r="C10" s="202"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="201" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="198"/>
-      <c r="C13" s="198"/>
-      <c r="D13" s="198"/>
-      <c r="E13" s="198"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="198"/>
-      <c r="B14" s="198"/>
-      <c r="C14" s="198"/>
-      <c r="D14" s="198"/>
-      <c r="E14" s="198"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="198"/>
-      <c r="B15" s="198"/>
-      <c r="C15" s="198"/>
-      <c r="D15" s="198"/>
-      <c r="E15" s="198"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="198"/>
-      <c r="B16" s="198"/>
-      <c r="C16" s="198"/>
-      <c r="D16" s="198"/>
-      <c r="E16" s="198"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="201"/>
+      <c r="C13" s="201"/>
+      <c r="D13" s="201"/>
+      <c r="E13" s="201"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="201"/>
+      <c r="B14" s="201"/>
+      <c r="C14" s="201"/>
+      <c r="D14" s="201"/>
+      <c r="E14" s="201"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="201"/>
+      <c r="B15" s="201"/>
+      <c r="C15" s="201"/>
+      <c r="D15" s="201"/>
+      <c r="E15" s="201"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="201"/>
+      <c r="B16" s="201"/>
+      <c r="C16" s="201"/>
+      <c r="D16" s="201"/>
+      <c r="E16" s="201"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>10</v>
       </c>
@@ -1962,7 +1965,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
         <v>36</v>
       </c>
@@ -1971,7 +1974,7 @@
       <c r="D21" s="35"/>
       <c r="E21" s="35"/>
     </row>
-    <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>81</v>
       </c>
@@ -1982,21 +1985,21 @@
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="162"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="162"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
@@ -2007,7 +2010,7 @@
       </c>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="59" t="s">
         <v>38</v>
       </c>
@@ -2020,7 +2023,7 @@
       <c r="E26" s="146"/>
       <c r="G26" s="22"/>
     </row>
-    <row r="27" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>49</v>
       </c>
@@ -2029,28 +2032,28 @@
       <c r="D27" s="162"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="29"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="162"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="162"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="173"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>44</v>
       </c>
@@ -2059,7 +2062,7 @@
       <c r="D31" s="173"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>43</v>
       </c>
@@ -2068,7 +2071,7 @@
       <c r="D32" s="173"/>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>39</v>
       </c>
@@ -2079,9 +2082,9 @@
       </c>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -2090,7 +2093,7 @@
       </c>
       <c r="E34" s="5"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="59" t="s">
         <v>38</v>
       </c>
@@ -2102,7 +2105,7 @@
       </c>
       <c r="E35" s="146"/>
     </row>
-    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="30" t="s">
         <v>1</v>
       </c>
@@ -2115,7 +2118,7 @@
       </c>
       <c r="F36" s="22"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="36" t="s">
         <v>19</v>
       </c>
@@ -2124,23 +2127,23 @@
       <c r="D37" s="176"/>
       <c r="E37" s="148"/>
     </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="194" t="s">
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="197" t="s">
         <v>121</v>
       </c>
-      <c r="B38" s="195"/>
+      <c r="B38" s="198"/>
       <c r="C38" s="54"/>
-      <c r="D38" s="162">
+      <c r="D38" s="192">
         <f>2*30000</f>
         <v>60000</v>
       </c>
       <c r="E38" s="149"/>
     </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="194" t="s">
-        <v>122</v>
-      </c>
-      <c r="B39" s="195"/>
+    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="197" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="198"/>
       <c r="C39" s="54"/>
       <c r="D39" s="177">
         <v>107000</v>
@@ -2148,7 +2151,7 @@
       <c r="E39" s="149"/>
       <c r="H39" s="160"/>
     </row>
-    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="30" t="s">
         <v>16</v>
       </c>
@@ -2160,7 +2163,7 @@
         <v>167000</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="36" t="s">
         <v>33</v>
       </c>
@@ -2169,29 +2172,29 @@
       <c r="D41" s="179"/>
       <c r="E41" s="151"/>
     </row>
-    <row r="42" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="192" t="s">
+    <row r="42" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="195" t="s">
         <v>84</v>
       </c>
-      <c r="B42" s="193"/>
+      <c r="B42" s="196"/>
       <c r="C42" s="56"/>
       <c r="D42" s="180">
         <v>71883</v>
       </c>
       <c r="E42" s="152"/>
     </row>
-    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="192" t="s">
+    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="195" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="193"/>
+      <c r="B43" s="196"/>
       <c r="C43" s="56"/>
       <c r="D43" s="181">
         <v>131172</v>
       </c>
       <c r="E43" s="152"/>
     </row>
-    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="30" t="s">
         <v>2</v>
       </c>
@@ -2203,7 +2206,7 @@
         <v>203055</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="36" t="s">
         <v>17</v>
       </c>
@@ -2212,21 +2215,21 @@
       <c r="D45" s="182"/>
       <c r="E45" s="155"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="54"/>
-      <c r="D46" s="183">
-        <v>781413.99</v>
+      <c r="D46" s="194">
+        <v>621996.29</v>
       </c>
       <c r="E46" s="163" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G46" s="128"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>87</v>
       </c>
@@ -2236,10 +2239,10 @@
         <v>10602.27</v>
       </c>
       <c r="E47" s="163" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>87</v>
       </c>
@@ -2254,50 +2257,50 @@
       </c>
       <c r="G48" s="144"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="166">
-        <v>111004.57</v>
+      <c r="D49" s="193">
+        <v>96171.08</v>
       </c>
       <c r="E49" s="163" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="str">
         <f>A49</f>
-        <v>Sindicatos mes de JULIO</v>
+        <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="166">
-        <v>7138.97</v>
+      <c r="D50" s="193">
+        <v>5681.31</v>
       </c>
       <c r="E50" s="164" t="str">
         <f>E49</f>
         <v>Debito 14/07</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="str">
         <f>A50</f>
-        <v>Sindicatos mes de JULIO</v>
+        <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="166">
-        <v>64250.7</v>
+      <c r="D51" s="193">
+        <v>51131.82</v>
       </c>
       <c r="E51" s="165" t="str">
         <f>E50</f>
         <v>Debito 14/07</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="30" t="s">
         <v>3</v>
       </c>
@@ -2306,10 +2309,10 @@
       <c r="D52" s="184"/>
       <c r="E52" s="153">
         <f>SUM(D46:D51)</f>
-        <v>1049942.79</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>861115.06</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="36" t="s">
         <v>18</v>
       </c>
@@ -2318,59 +2321,59 @@
       <c r="D53" s="182"/>
       <c r="E53" s="155"/>
     </row>
-    <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="166">
-        <v>52544.74</v>
+        <v>52825.87</v>
       </c>
       <c r="E54" s="163" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>89</v>
       </c>
       <c r="B55" s="166"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="166">
-        <v>23727.17</v>
+      <c r="D55" s="193">
+        <v>23726.77</v>
       </c>
       <c r="E55" s="163" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="166">
-        <v>32112.78</v>
+      <c r="D56" s="193">
+        <v>27113.49</v>
       </c>
       <c r="E56" s="163" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="192" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="195" t="s">
         <v>82</v>
       </c>
-      <c r="B57" s="193"/>
+      <c r="B57" s="196"/>
       <c r="C57" s="5"/>
       <c r="D57" s="166">
         <v>355815.42</v>
       </c>
       <c r="E57" s="163" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="30" t="s">
         <v>4</v>
       </c>
@@ -2379,19 +2382,19 @@
       <c r="D58" s="185"/>
       <c r="E58" s="153">
         <f>SUM(D54:D57)</f>
-        <v>464200.11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>459481.55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="36"/>
       <c r="B59" s="30"/>
       <c r="C59" s="30"/>
       <c r="D59" s="178"/>
       <c r="E59" s="156"/>
     </row>
-    <row r="60" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="169" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="B60" s="161"/>
       <c r="C60" s="5"/>
@@ -2399,23 +2402,23 @@
         <v>54500</v>
       </c>
       <c r="E60" s="167" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="194" t="s">
-        <v>112</v>
-      </c>
-      <c r="B61" s="195"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="197" t="s">
+        <v>106</v>
+      </c>
+      <c r="B61" s="198"/>
       <c r="C61" s="5"/>
       <c r="D61" s="166">
         <v>129500</v>
       </c>
       <c r="E61" s="167" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="187" t="s">
         <v>96</v>
       </c>
@@ -2425,77 +2428,77 @@
         <v>59450</v>
       </c>
       <c r="E62" s="168" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="194" t="s">
-        <v>119</v>
-      </c>
-      <c r="B63" s="195"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="197" t="s">
+        <v>112</v>
+      </c>
+      <c r="B63" s="198"/>
       <c r="C63" s="5"/>
       <c r="D63" s="110">
         <v>44480.41</v>
       </c>
       <c r="E63" s="167" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="194" t="s">
-        <v>119</v>
-      </c>
-      <c r="B64" s="195"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="197" t="s">
+        <v>112</v>
+      </c>
+      <c r="B64" s="198"/>
       <c r="C64" s="5"/>
       <c r="D64" s="110">
         <v>9580</v>
       </c>
       <c r="E64" s="167" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="194" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="197" t="s">
         <v>97</v>
       </c>
-      <c r="B65" s="195"/>
+      <c r="B65" s="198"/>
       <c r="C65" s="5"/>
       <c r="D65" s="110">
         <v>35000</v>
       </c>
       <c r="E65" s="168" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="192" t="s">
-        <v>114</v>
-      </c>
-      <c r="B66" s="193"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="195" t="s">
+        <v>119</v>
+      </c>
+      <c r="B66" s="196"/>
       <c r="C66" s="5"/>
       <c r="D66" s="110">
         <v>85000</v>
       </c>
       <c r="E66" s="191" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="192" t="s">
-        <v>107</v>
-      </c>
-      <c r="B67" s="193"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="195" t="s">
+        <v>120</v>
+      </c>
+      <c r="B67" s="196"/>
       <c r="C67" s="5"/>
       <c r="D67" s="110">
         <v>250000</v>
       </c>
       <c r="E67" s="191" t="s">
-        <v>106</v>
-      </c>
-      <c r="I67" s="192"/>
-      <c r="J67" s="193"/>
-    </row>
-    <row r="68" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+      <c r="I67" s="195"/>
+      <c r="J67" s="196"/>
+    </row>
+    <row r="68" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="30" t="s">
         <v>9</v>
       </c>
@@ -2507,7 +2510,7 @@
         <v>667510.41</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="36" t="s">
         <v>12</v>
       </c>
@@ -2516,9 +2519,9 @@
       <c r="D69" s="175"/>
       <c r="E69" s="156"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -2527,9 +2530,9 @@
       </c>
       <c r="E70" s="158"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -2538,7 +2541,7 @@
       </c>
       <c r="E71" s="41"/>
     </row>
-    <row r="72" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="53" t="s">
         <v>16</v>
       </c>
@@ -2550,14 +2553,14 @@
         <v>106598.95</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="106"/>
       <c r="E73" s="114"/>
     </row>
-    <row r="74" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="31" t="s">
         <v>55</v>
       </c>
@@ -2566,13 +2569,13 @@
       <c r="D74" s="115"/>
       <c r="E74" s="116"/>
     </row>
-    <row r="75" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="D75" s="117"/>
       <c r="E75" s="118"/>
       <c r="F75" s="45"/>
     </row>
-    <row r="76" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>13</v>
       </c>
@@ -2581,21 +2584,21 @@
       <c r="D76" s="119"/>
       <c r="E76" s="120">
         <f>(SUM(E29:E74))</f>
-        <v>3665345.2600000002</v>
+        <v>3471798.97</v>
       </c>
       <c r="F76" s="144"/>
       <c r="G76" s="45"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D77" s="117"/>
       <c r="E77" s="117"/>
     </row>
-    <row r="78" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D78" s="117"/>
       <c r="E78" s="117"/>
       <c r="H78" s="186"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
         <v>50</v>
       </c>
@@ -2604,35 +2607,35 @@
       <c r="D79" s="121"/>
       <c r="E79" s="122"/>
     </row>
-    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="192"/>
-      <c r="B80" s="193"/>
+    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="195"/>
+      <c r="B80" s="196"/>
       <c r="C80" s="5"/>
       <c r="D80" s="132"/>
       <c r="E80" s="108"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="192"/>
-      <c r="B81" s="193"/>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="195"/>
+      <c r="B81" s="196"/>
       <c r="C81" s="5"/>
       <c r="D81" s="110"/>
       <c r="E81" s="108"/>
     </row>
-    <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="194"/>
-      <c r="B82" s="195"/>
+    <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="197"/>
+      <c r="B82" s="198"/>
       <c r="C82" s="5"/>
       <c r="D82" s="110"/>
       <c r="E82" s="108"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="109"/>
       <c r="B83" s="111"/>
       <c r="C83" s="5"/>
       <c r="D83" s="110"/>
       <c r="E83" s="108"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="51"/>
       <c r="B84" s="50"/>
       <c r="C84" s="50"/>
@@ -2642,9 +2645,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="31" t="s">
         <v>20</v>
       </c>
@@ -2653,8 +2656,8 @@
       <c r="D87" s="32"/>
       <c r="E87" s="105"/>
     </row>
-    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>21</v>
       </c>
@@ -2666,26 +2669,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="91" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="103" t="s">
         <v>14</v>
       </c>
       <c r="B91" s="104">
         <f>E76</f>
-        <v>3665345.2600000002</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3471798.97</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="103" t="s">
         <v>15</v>
       </c>
       <c r="B92" s="104">
         <f>E76-E74</f>
-        <v>3665345.2600000002</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3471798.97</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="103" t="s">
         <v>22</v>
       </c>
@@ -2694,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="103" t="s">
         <v>45</v>
       </c>
@@ -2703,44 +2706,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="200"/>
-      <c r="B97" s="200"/>
-      <c r="C97" s="200"/>
-      <c r="D97" s="200"/>
-      <c r="E97" s="200"/>
-    </row>
-    <row r="98" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="200"/>
-      <c r="B98" s="200"/>
-      <c r="C98" s="200"/>
-      <c r="D98" s="200"/>
-      <c r="E98" s="200"/>
-    </row>
-    <row r="99" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="200"/>
-      <c r="B99" s="200"/>
-      <c r="C99" s="200"/>
-      <c r="D99" s="200"/>
-      <c r="E99" s="200"/>
-    </row>
-    <row r="101" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="203"/>
+      <c r="B97" s="203"/>
+      <c r="C97" s="203"/>
+      <c r="D97" s="203"/>
+      <c r="E97" s="203"/>
+    </row>
+    <row r="98" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="203"/>
+      <c r="B98" s="203"/>
+      <c r="C98" s="203"/>
+      <c r="D98" s="203"/>
+      <c r="E98" s="203"/>
+    </row>
+    <row r="99" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="203"/>
+      <c r="B99" s="203"/>
+      <c r="C99" s="203"/>
+      <c r="D99" s="203"/>
+      <c r="E99" s="203"/>
+    </row>
+    <row r="101" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
         <v>35</v>
       </c>
       <c r="B101" s="129"/>
       <c r="C101" s="24"/>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="34"/>
       <c r="B102" s="61">
         <v>0</v>
       </c>
       <c r="C102" s="26"/>
     </row>
-    <row r="103" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="25" t="s">
         <v>7</v>
       </c>
@@ -2750,14 +2753,14 @@
       </c>
       <c r="C103" s="24"/>
     </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="25"/>
       <c r="B104" s="41">
         <v>0</v>
       </c>
       <c r="C104" s="24"/>
     </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="25" t="s">
         <v>46</v>
       </c>
@@ -2767,29 +2770,29 @@
       </c>
       <c r="C105" s="24"/>
     </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="28"/>
       <c r="B106" s="49"/>
       <c r="C106" s="24"/>
     </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="127" t="s">
         <v>51</v>
       </c>
       <c r="B107" s="49"/>
       <c r="C107" s="24"/>
     </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="40" t="s">
         <v>23</v>
       </c>
       <c r="B108" s="49">
         <f>-B92</f>
-        <v>-3665345.2600000002</v>
+        <v>-3471798.97</v>
       </c>
       <c r="C108" s="24"/>
     </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="28" t="s">
         <v>24</v>
       </c>
@@ -2799,34 +2802,34 @@
       </c>
       <c r="C109" s="24"/>
     </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B110" s="61">
         <f>SUM(B102:B109)</f>
-        <v>-639411.56999999937</v>
+        <v>-445865.27999999933</v>
       </c>
       <c r="C110" s="27"/>
       <c r="D110" s="45"/>
     </row>
-    <row r="111" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="42"/>
       <c r="C111" s="27"/>
       <c r="D111" s="45"/>
       <c r="E111" s="130"/>
       <c r="F111" s="131"/>
     </row>
-    <row r="112" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="43"/>
       <c r="C112" s="27"/>
     </row>
-    <row r="113" spans="1:13" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113"/>
       <c r="B113" s="42"/>
       <c r="C113" s="38"/>
     </row>
-    <row r="114" spans="1:13" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A114" s="135" t="s">
         <v>95</v>
       </c>
@@ -2836,16 +2839,16 @@
       <c r="C114" s="38"/>
       <c r="D114" s="48"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="56" t="s">
         <v>56</v>
       </c>
       <c r="B115" s="141">
         <f>-B92</f>
-        <v>-3665345.2600000002</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+        <v>-3471798.97</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="56" t="s">
         <v>57</v>
       </c>
@@ -2854,7 +2857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="56" t="s">
         <v>93</v>
       </c>
@@ -2863,7 +2866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="56" t="s">
         <v>58</v>
       </c>
@@ -2872,39 +2875,39 @@
         <v>3025933.6900000009</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="143" t="s">
         <v>59</v>
       </c>
       <c r="B119" s="189"/>
     </row>
-    <row r="120" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="139" t="s">
         <v>53</v>
       </c>
       <c r="B120" s="140">
         <f>SUM(B114:C119)</f>
-        <v>-726690.58609999763</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+        <v>-533144.29609999759</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="137"/>
       <c r="B121" s="137"/>
     </row>
-    <row r="122" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="201" t="s">
+    <row r="122" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A123" s="204" t="s">
         <v>34</v>
       </c>
-      <c r="B123" s="201"/>
-      <c r="C123" s="201"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="201"/>
-      <c r="B124" s="201"/>
-      <c r="C124" s="201"/>
-    </row>
-    <row r="125" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="204"/>
+      <c r="C123" s="204"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A124" s="204"/>
+      <c r="B124" s="204"/>
+      <c r="C124" s="204"/>
+    </row>
+    <row r="125" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="124"/>
       <c r="B125" s="37"/>
       <c r="C125" s="37">
@@ -2912,13 +2915,13 @@
       </c>
       <c r="E125" s="144"/>
     </row>
-    <row r="126" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="124"/>
       <c r="B126" s="126"/>
       <c r="C126" s="123"/>
       <c r="D126" s="144"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="46" t="s">
         <v>9</v>
       </c>
@@ -2928,36 +2931,36 @@
       </c>
       <c r="C127" s="47"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M128" s="8"/>
     </row>
-    <row r="129" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="200"/>
-      <c r="B129" s="200"/>
-      <c r="C129" s="200"/>
-      <c r="D129" s="200"/>
-      <c r="E129" s="200"/>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="200"/>
-      <c r="B130" s="200"/>
-      <c r="C130" s="200"/>
-      <c r="D130" s="200"/>
-      <c r="E130" s="200"/>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="200"/>
-      <c r="B131" s="200"/>
-      <c r="C131" s="200"/>
-      <c r="D131" s="200"/>
-      <c r="E131" s="200"/>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="200"/>
-      <c r="B132" s="200"/>
-      <c r="C132" s="200"/>
-      <c r="D132" s="200"/>
-      <c r="E132" s="200"/>
+    <row r="129" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="203"/>
+      <c r="B129" s="203"/>
+      <c r="C129" s="203"/>
+      <c r="D129" s="203"/>
+      <c r="E129" s="203"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" s="203"/>
+      <c r="B130" s="203"/>
+      <c r="C130" s="203"/>
+      <c r="D130" s="203"/>
+      <c r="E130" s="203"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="203"/>
+      <c r="B131" s="203"/>
+      <c r="C131" s="203"/>
+      <c r="D131" s="203"/>
+      <c r="E131" s="203"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="203"/>
+      <c r="B132" s="203"/>
+      <c r="C132" s="203"/>
+      <c r="D132" s="203"/>
+      <c r="E132" s="203"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -2992,46 +2995,46 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="0.140625" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
-    <col min="14" max="14" width="0.42578125" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" customWidth="1"/>
-    <col min="16" max="16" width="0.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="0.109375" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="0.44140625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" customWidth="1"/>
+    <col min="16" max="16" width="0.109375" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
-      <c r="M1" s="202"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="205"/>
+      <c r="M1" s="205"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3057,7 +3060,7 @@
       <c r="O2" s="57"/>
       <c r="P2" s="22"/>
     </row>
-    <row r="3" spans="1:18" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3074,75 +3077,75 @@
       <c r="N3" s="58"/>
       <c r="O3" s="62"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="207" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="207" t="s">
+      <c r="B4" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="210" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="D4" s="210" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="203" t="s">
+      <c r="E4" s="206" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="207" t="s">
+      <c r="F4" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="207" t="s">
+      <c r="G4" s="210" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="209" t="s">
+      <c r="H4" s="212" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="203" t="s">
+      <c r="I4" s="206" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="203" t="s">
+      <c r="J4" s="206" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="203" t="s">
+      <c r="K4" s="206" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="212" t="s">
+      <c r="L4" s="215" t="s">
         <v>90</v>
       </c>
       <c r="M4" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="205" t="s">
+      <c r="N4" s="208" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="214" t="s">
+      <c r="O4" s="217" t="s">
         <v>40</v>
       </c>
       <c r="R4" s="45"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="208"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="208"/>
-      <c r="E5" s="204"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="216"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="211"/>
-      <c r="K5" s="204"/>
-      <c r="L5" s="213"/>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="211"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="219"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="214"/>
+      <c r="K5" s="207"/>
+      <c r="L5" s="216"/>
       <c r="M5" s="63" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 14/08</v>
-      </c>
-      <c r="N5" s="206"/>
-      <c r="O5" s="215"/>
-    </row>
-    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>VTO 15/09</v>
+      </c>
+      <c r="N5" s="209"/>
+      <c r="O5" s="218"/>
+    </row>
+    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="66">
         <v>1</v>
       </c>
@@ -3196,7 +3199,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="66">
         <f>A6+1</f>
         <v>2</v>
@@ -3252,7 +3255,7 @@
       </c>
       <c r="Q7" s="45"/>
     </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66">
         <f t="shared" ref="A8:A23" si="7">A7+1</f>
         <v>3</v>
@@ -3308,7 +3311,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="66">
         <f t="shared" si="7"/>
         <v>4</v>
@@ -3365,7 +3368,7 @@
       </c>
       <c r="R9" s="45"/>
     </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="66">
         <f t="shared" si="7"/>
         <v>5</v>
@@ -3422,7 +3425,7 @@
       </c>
       <c r="R10" s="45"/>
     </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="66">
         <f t="shared" si="7"/>
         <v>6</v>
@@ -3478,7 +3481,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="66">
         <f t="shared" si="7"/>
         <v>7</v>
@@ -3534,7 +3537,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="66">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -3593,7 +3596,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="66">
         <f t="shared" si="7"/>
         <v>9</v>
@@ -3649,7 +3652,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="66">
         <f t="shared" si="7"/>
         <v>10</v>
@@ -3705,7 +3708,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="66">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -3761,7 +3764,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="66">
         <f t="shared" si="7"/>
         <v>12</v>
@@ -3817,7 +3820,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="66">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -3873,7 +3876,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="66">
         <f t="shared" si="7"/>
         <v>14</v>
@@ -3929,7 +3932,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="66">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -3985,7 +3988,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="66">
         <f t="shared" si="7"/>
         <v>16</v>
@@ -4042,7 +4045,7 @@
       </c>
       <c r="R21" s="44"/>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="66">
         <f t="shared" si="7"/>
         <v>17</v>
@@ -4098,7 +4101,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="66">
         <f t="shared" si="7"/>
         <v>18</v>
@@ -4155,7 +4158,7 @@
       </c>
       <c r="R23" s="145"/>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="66"/>
       <c r="B24" s="66"/>
       <c r="C24" s="67"/>
@@ -4176,7 +4179,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="86"/>
       <c r="B25" s="66"/>
       <c r="C25" s="67"/>
@@ -4194,7 +4197,7 @@
       <c r="O25" s="85"/>
       <c r="P25" s="45"/>
     </row>
-    <row r="26" spans="1:18" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="86"/>
       <c r="B26" s="68"/>
       <c r="C26" s="67"/>
@@ -4212,7 +4215,7 @@
       <c r="O26" s="85"/>
       <c r="P26" s="45"/>
     </row>
-    <row r="27" spans="1:18" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="87"/>
       <c r="B27" s="66"/>
       <c r="C27" s="67"/>
@@ -4230,7 +4233,7 @@
       <c r="O27" s="85"/>
       <c r="P27" s="45"/>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="66"/>
       <c r="B28" s="94"/>
       <c r="C28" s="94"/>
@@ -4248,7 +4251,7 @@
       <c r="O28" s="97"/>
       <c r="P28" s="45"/>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="98"/>
       <c r="B29" s="99"/>
       <c r="C29" s="99"/>
@@ -4301,97 +4304,97 @@
         <v>3458249.7100000004</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="52"/>
       <c r="C30" s="52"/>
     </row>
-    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="200" t="str">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="203" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="200"/>
-      <c r="D32" s="200"/>
-      <c r="E32" s="200"/>
-      <c r="F32" s="200"/>
-      <c r="G32" s="200"/>
-      <c r="H32" s="200"/>
-      <c r="I32" s="200"/>
-      <c r="J32" s="200"/>
-      <c r="K32" s="200"/>
-      <c r="L32" s="200"/>
-      <c r="M32" s="200"/>
-    </row>
-    <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="200"/>
-      <c r="C33" s="200"/>
-      <c r="D33" s="200"/>
-      <c r="E33" s="200"/>
-      <c r="F33" s="200"/>
-      <c r="G33" s="200"/>
-      <c r="H33" s="200"/>
-      <c r="I33" s="200"/>
-      <c r="J33" s="200"/>
-      <c r="K33" s="200"/>
-      <c r="L33" s="200"/>
-      <c r="M33" s="200"/>
-    </row>
-    <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="200"/>
-      <c r="C34" s="200"/>
-      <c r="D34" s="200"/>
-      <c r="E34" s="200"/>
-      <c r="F34" s="200"/>
-      <c r="G34" s="200"/>
-      <c r="H34" s="200"/>
-      <c r="I34" s="200"/>
-      <c r="J34" s="200"/>
-      <c r="K34" s="200"/>
-      <c r="L34" s="200"/>
-      <c r="M34" s="200"/>
-    </row>
-    <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="200"/>
-      <c r="C35" s="200"/>
-      <c r="D35" s="200"/>
-      <c r="E35" s="200"/>
-      <c r="F35" s="200"/>
-      <c r="G35" s="200"/>
-      <c r="H35" s="200"/>
-      <c r="I35" s="200"/>
-      <c r="J35" s="200"/>
-      <c r="K35" s="200"/>
-      <c r="L35" s="200"/>
-      <c r="M35" s="200"/>
-    </row>
-    <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="200"/>
-      <c r="C36" s="200"/>
-      <c r="D36" s="200"/>
-      <c r="E36" s="200"/>
-      <c r="F36" s="200"/>
-      <c r="G36" s="200"/>
-      <c r="H36" s="200"/>
-      <c r="I36" s="200"/>
-      <c r="J36" s="200"/>
-      <c r="K36" s="200"/>
-      <c r="L36" s="200"/>
-      <c r="M36" s="200"/>
-    </row>
-    <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="200"/>
-      <c r="C37" s="200"/>
-      <c r="D37" s="200"/>
-      <c r="E37" s="200"/>
-      <c r="F37" s="200"/>
-      <c r="G37" s="200"/>
-      <c r="H37" s="200"/>
-      <c r="I37" s="200"/>
-      <c r="J37" s="200"/>
-      <c r="K37" s="200"/>
-      <c r="L37" s="200"/>
-      <c r="M37" s="200"/>
+      <c r="C32" s="203"/>
+      <c r="D32" s="203"/>
+      <c r="E32" s="203"/>
+      <c r="F32" s="203"/>
+      <c r="G32" s="203"/>
+      <c r="H32" s="203"/>
+      <c r="I32" s="203"/>
+      <c r="J32" s="203"/>
+      <c r="K32" s="203"/>
+      <c r="L32" s="203"/>
+      <c r="M32" s="203"/>
+    </row>
+    <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="203"/>
+      <c r="C33" s="203"/>
+      <c r="D33" s="203"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="203"/>
+      <c r="G33" s="203"/>
+      <c r="H33" s="203"/>
+      <c r="I33" s="203"/>
+      <c r="J33" s="203"/>
+      <c r="K33" s="203"/>
+      <c r="L33" s="203"/>
+      <c r="M33" s="203"/>
+    </row>
+    <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="203"/>
+      <c r="C34" s="203"/>
+      <c r="D34" s="203"/>
+      <c r="E34" s="203"/>
+      <c r="F34" s="203"/>
+      <c r="G34" s="203"/>
+      <c r="H34" s="203"/>
+      <c r="I34" s="203"/>
+      <c r="J34" s="203"/>
+      <c r="K34" s="203"/>
+      <c r="L34" s="203"/>
+      <c r="M34" s="203"/>
+    </row>
+    <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="203"/>
+      <c r="C35" s="203"/>
+      <c r="D35" s="203"/>
+      <c r="E35" s="203"/>
+      <c r="F35" s="203"/>
+      <c r="G35" s="203"/>
+      <c r="H35" s="203"/>
+      <c r="I35" s="203"/>
+      <c r="J35" s="203"/>
+      <c r="K35" s="203"/>
+      <c r="L35" s="203"/>
+      <c r="M35" s="203"/>
+    </row>
+    <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="203"/>
+      <c r="C36" s="203"/>
+      <c r="D36" s="203"/>
+      <c r="E36" s="203"/>
+      <c r="F36" s="203"/>
+      <c r="G36" s="203"/>
+      <c r="H36" s="203"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="203"/>
+      <c r="K36" s="203"/>
+      <c r="L36" s="203"/>
+      <c r="M36" s="203"/>
+    </row>
+    <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="203"/>
+      <c r="C37" s="203"/>
+      <c r="D37" s="203"/>
+      <c r="E37" s="203"/>
+      <c r="F37" s="203"/>
+      <c r="G37" s="203"/>
+      <c r="H37" s="203"/>
+      <c r="I37" s="203"/>
+      <c r="J37" s="203"/>
+      <c r="K37" s="203"/>
+      <c r="L37" s="203"/>
+      <c r="M37" s="203"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -4420,9 +4423,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="C5:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C5" s="190" t="s">
         <v>98</v>
       </c>

--- a/YRIGOYEN 9730/Agosto/YRIGOYEN7630-Agosto.xlsx
+++ b/YRIGOYEN 9730/Agosto/YRIGOYEN7630-Agosto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\YRIGOYEN 9730\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9730\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866069E8-1B42-435A-9C3C-E702A9128657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E06E4A5-86E9-4813-B3C4-27B96EBB15C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,15 +18,15 @@
     <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$128</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$121</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="116">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -112,9 +112,6 @@
     <t>Inquilinos</t>
   </si>
   <si>
-    <t>Pago por</t>
-  </si>
-  <si>
     <t>CUIT ADMINISTRACION: 27231256879</t>
   </si>
   <si>
@@ -137,9 +134,6 @@
   </si>
   <si>
     <t>HABERES ENCARGADOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retenciones </t>
   </si>
   <si>
     <t>Neto</t>
@@ -281,12 +275,6 @@
     <t>EDESUR - Cliente nro. 1481147</t>
   </si>
   <si>
-    <t>Zurich Seguro Integral consorcio</t>
-  </si>
-  <si>
-    <t>Allianz - Seguro de vida</t>
-  </si>
-  <si>
     <t xml:space="preserve">CBU: 0440060830000011423569                                                                                                          / ALIAS: OMBU.TECLEO.AMOROSAS /                                            TELEFONO: 11 5320-2676  </t>
   </si>
   <si>
@@ -317,57 +305,18 @@
     <t>SALDO EN BANCO</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
-    <t>Fumigaciones Lanus - Servicio de fumigacion - Mes de abril</t>
-  </si>
-  <si>
     <t>laurasmiet@gmail.com</t>
   </si>
   <si>
     <t>AGREGAR A LA CADENA</t>
   </si>
   <si>
-    <t>Transf 17/7</t>
-  </si>
-  <si>
-    <t>Transf 14/07</t>
-  </si>
-  <si>
-    <t>Transf 10/07</t>
-  </si>
-  <si>
-    <t>Debito 14/07</t>
-  </si>
-  <si>
-    <t>Debito 07/07</t>
-  </si>
-  <si>
-    <t>Efectivo 07/07</t>
-  </si>
-  <si>
-    <t>Matafuegos - Recarga anual</t>
-  </si>
-  <si>
-    <t>Debito 16/07</t>
-  </si>
-  <si>
-    <t>Transf 25/07</t>
-  </si>
-  <si>
-    <t>Transf 30/07</t>
-  </si>
-  <si>
     <t>Sra Fernanda Reemplazo por vacaciones</t>
   </si>
   <si>
     <t>Gastos bancarios</t>
   </si>
   <si>
-    <t>Ferreteria - compra de materiales para obra - caños</t>
-  </si>
-  <si>
     <t>Mantenimiento de cuenta</t>
   </si>
   <si>
@@ -386,16 +335,46 @@
     <t>Sindicatos mes de AGOSTO</t>
   </si>
   <si>
-    <t>AGOSTO Doartero - Visita inspeccion hidraulica</t>
-  </si>
-  <si>
-    <t>AGOSTO Doartero - Cambio de caño cloacal UF 14</t>
-  </si>
-  <si>
     <t>Gustavo padron - Sr contador honorarios JULIO y AGOSTO</t>
   </si>
   <si>
-    <t>Ascensores lema - Mantenimiento JULIO</t>
+    <t>Megasec - compra de bastago de polvo y manometro</t>
+  </si>
+  <si>
+    <t>Transf 26/08</t>
+  </si>
+  <si>
+    <t>Subidos en Agost000</t>
+  </si>
+  <si>
+    <t>Federacion patronal - Seguro de vida Poliza nro. 211840604</t>
+  </si>
+  <si>
+    <t>Federacion patronal  Seguro obligatorio de consorcio</t>
+  </si>
+  <si>
+    <t>Debito 07/08</t>
+  </si>
+  <si>
+    <t>Debito 18/08</t>
+  </si>
+  <si>
+    <t>Ascensores lema - Mantenimiento Julio</t>
+  </si>
+  <si>
+    <t>Transf 29/08</t>
+  </si>
+  <si>
+    <t>PENDIENTE PASAR COSAS DE DOARTERO ARREGLO DPTO AGUSTIN</t>
+  </si>
+  <si>
+    <t>Debito 03/08</t>
+  </si>
+  <si>
+    <t>Debito 04/08</t>
+  </si>
+  <si>
+    <t>Debito 02/08</t>
   </si>
 </sst>
 </file>
@@ -403,14 +382,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="29" x14ac:knownFonts="1">
     <font>
@@ -1109,11 +1088,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1121,7 +1100,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1136,9 +1115,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1153,7 +1132,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1163,40 +1142,40 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1210,7 +1189,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1218,177 +1197,165 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="11" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="25" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="25" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="26" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1829,134 +1796,134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M132"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M125"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="15"/>
       <c r="B1" s="71" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C1" s="71"/>
       <c r="D1" s="71"/>
       <c r="E1" s="72"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="73"/>
       <c r="D2" s="73"/>
       <c r="E2" s="74"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="199" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="200"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="192"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="102" t="s">
-        <v>42</v>
+      <c r="B4" s="101" t="s">
+        <v>40</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="73" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="202" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="202"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="202"/>
-      <c r="C10" s="202"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="201" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="201"/>
-      <c r="C13" s="201"/>
-      <c r="D13" s="201"/>
-      <c r="E13" s="201"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="201"/>
-      <c r="B14" s="201"/>
-      <c r="C14" s="201"/>
-      <c r="D14" s="201"/>
-      <c r="E14" s="201"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="201"/>
-      <c r="B15" s="201"/>
-      <c r="C15" s="201"/>
-      <c r="D15" s="201"/>
-      <c r="E15" s="201"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="201"/>
-      <c r="B16" s="201"/>
-      <c r="C16" s="201"/>
-      <c r="D16" s="201"/>
-      <c r="E16" s="201"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="194" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="194"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="194"/>
+      <c r="C9" s="194"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="194"/>
+      <c r="C10" s="194"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="193"/>
+      <c r="C13" s="193"/>
+      <c r="D13" s="193"/>
+      <c r="E13" s="193"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="193"/>
+      <c r="B14" s="193"/>
+      <c r="C14" s="193"/>
+      <c r="D14" s="193"/>
+      <c r="E14" s="193"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="193"/>
+      <c r="B15" s="193"/>
+      <c r="C15" s="193"/>
+      <c r="D15" s="193"/>
+      <c r="E15" s="193"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="193"/>
+      <c r="B16" s="193"/>
+      <c r="C16" s="193"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>10</v>
       </c>
@@ -1965,1026 +1932,946 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="36"/>
       <c r="C21" s="36"/>
       <c r="D21" s="35"/>
       <c r="E21" s="35"/>
     </row>
-    <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="162">
-        <v>855038</v>
+      <c r="D22" s="160">
+        <v>773598</v>
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="162"/>
+      <c r="D23" s="160"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="162"/>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="169">
+        <f>SUM(D22:D23)</f>
+        <v>773598</v>
+      </c>
+      <c r="E24" s="144"/>
+      <c r="G24" s="22"/>
+    </row>
+    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="162">
-        <v>0</v>
-      </c>
+      <c r="D25" s="160"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="59" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="172">
-        <f>SUM(D22:D25)</f>
-        <v>855038</v>
-      </c>
-      <c r="E26" s="146"/>
-      <c r="G26" s="22"/>
-    </row>
-    <row r="27" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
-        <v>49</v>
-      </c>
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="29"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="160"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="162"/>
+      <c r="D27" s="160"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="29"/>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="162"/>
+      <c r="D28" s="170"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
+    <row r="29" spans="1:7" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="162"/>
+      <c r="D29" s="170"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="173"/>
+      <c r="D30" s="170"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="173"/>
+      <c r="D31" s="170">
+        <v>0</v>
+      </c>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="173"/>
+      <c r="D32" s="170">
+        <v>28000</v>
+      </c>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="173">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="173">
-        <v>152000</v>
-      </c>
-      <c r="E34" s="5"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="59" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="59"/>
-      <c r="C35" s="59"/>
-      <c r="D35" s="174">
-        <f>SUM(D27:D34)</f>
-        <v>152000</v>
-      </c>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="59"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="171">
+        <f>SUM(D25:D32)</f>
+        <v>28000</v>
+      </c>
+      <c r="E33" s="144"/>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="172"/>
+      <c r="E34" s="145">
+        <f>D24+D33</f>
+        <v>801598</v>
+      </c>
+      <c r="F34" s="22"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="173"/>
       <c r="E35" s="146"/>
     </row>
-    <row r="36" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="175"/>
-      <c r="E36" s="147">
-        <f>D26+D35</f>
-        <v>1007038</v>
-      </c>
-      <c r="F36" s="22"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="176"/>
-      <c r="E37" s="148"/>
-    </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="197" t="s">
-        <v>121</v>
-      </c>
-      <c r="B38" s="198"/>
-      <c r="C38" s="54"/>
-      <c r="D38" s="192">
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="189" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="190"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="160">
         <f>2*30000</f>
         <v>60000</v>
       </c>
-      <c r="E38" s="149"/>
-    </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="197" t="s">
+      <c r="E36" s="147"/>
+    </row>
+    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="189" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" s="190"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="174">
+        <v>112400</v>
+      </c>
+      <c r="E37" s="147"/>
+      <c r="H37" s="158" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="175"/>
+      <c r="E38" s="148">
+        <f>SUM(D36:D37)</f>
+        <v>172400</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="176"/>
+      <c r="E39" s="149"/>
+    </row>
+    <row r="40" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="187" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="188"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="177">
+        <v>26570</v>
+      </c>
+      <c r="E40" s="161" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="198"/>
-      <c r="C39" s="54"/>
-      <c r="D39" s="177">
-        <v>107000</v>
-      </c>
-      <c r="E39" s="149"/>
-      <c r="H39" s="160"/>
-    </row>
-    <row r="40" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="178"/>
-      <c r="E40" s="150">
-        <f>SUM(D38:D39)</f>
-        <v>167000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="179"/>
-      <c r="E41" s="151"/>
-    </row>
-    <row r="42" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="195" t="s">
-        <v>84</v>
-      </c>
-      <c r="B42" s="196"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="180">
-        <v>71883</v>
-      </c>
-      <c r="E42" s="152"/>
-    </row>
-    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="195" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" s="196"/>
-      <c r="C43" s="56"/>
-      <c r="D43" s="181">
-        <v>131172</v>
-      </c>
-      <c r="E43" s="152"/>
-    </row>
-    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="30" t="s">
+    </row>
+    <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="187" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="188"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="178">
+        <v>54278</v>
+      </c>
+      <c r="E41" s="150" t="str">
+        <f>E40</f>
+        <v>Debito 04/08</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="178"/>
-      <c r="E44" s="153">
-        <f>SUM(D42:D43)</f>
-        <v>203055</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="36" t="s">
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="175"/>
+      <c r="E42" s="151">
+        <f>SUM(D40:D41)</f>
+        <v>80848</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="154"/>
-      <c r="C45" s="154"/>
-      <c r="D45" s="182"/>
-      <c r="E45" s="155"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="179"/>
+      <c r="E43" s="153"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="180">
+        <v>621996.29</v>
+      </c>
+      <c r="E44" s="161" t="s">
+        <v>99</v>
+      </c>
+      <c r="G44" s="127"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="180">
+        <v>10602.27</v>
+      </c>
+      <c r="E45" s="161" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="54"/>
-      <c r="D46" s="194">
-        <v>621996.29</v>
-      </c>
-      <c r="E46" s="163" t="s">
-        <v>116</v>
-      </c>
-      <c r="G46" s="128"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D46" s="180">
+        <v>75532.289999999994</v>
+      </c>
+      <c r="E46" s="161" t="str">
+        <f>E45</f>
+        <v>Debito 18/08</v>
+      </c>
+      <c r="G46" s="143"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="B47" s="5"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="183">
-        <v>10602.27</v>
-      </c>
-      <c r="E47" s="163" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>87</v>
+      <c r="C47" s="5"/>
+      <c r="D47" s="164">
+        <v>86171.08</v>
+      </c>
+      <c r="E47" s="161" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="str">
+        <f>A47</f>
+        <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B48" s="5"/>
-      <c r="C48" s="54"/>
-      <c r="D48" s="183">
-        <v>75532.289999999994</v>
-      </c>
-      <c r="E48" s="163" t="str">
+      <c r="C48" s="5"/>
+      <c r="D48" s="164">
+        <v>5681.31</v>
+      </c>
+      <c r="E48" s="162" t="str">
         <f>E47</f>
-        <v>Debito 16/07</v>
-      </c>
-      <c r="G48" s="144"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
-        <v>118</v>
+        <v>Debito 12/08</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="str">
+        <f>A48</f>
+        <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="193">
-        <v>96171.08</v>
-      </c>
-      <c r="E49" s="163" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="str">
-        <f>A49</f>
-        <v>Sindicatos mes de AGOSTO</v>
-      </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="193">
-        <v>5681.31</v>
-      </c>
-      <c r="E50" s="164" t="str">
-        <f>E49</f>
-        <v>Debito 14/07</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="str">
-        <f>A50</f>
-        <v>Sindicatos mes de AGOSTO</v>
-      </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="193">
+      <c r="D49" s="164">
         <v>51131.82</v>
       </c>
-      <c r="E51" s="165" t="str">
-        <f>E50</f>
-        <v>Debito 14/07</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="30" t="s">
+      <c r="E49" s="163" t="str">
+        <f>E48</f>
+        <v>Debito 12/08</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B52" s="154"/>
-      <c r="C52" s="154"/>
-      <c r="D52" s="184"/>
-      <c r="E52" s="153">
-        <f>SUM(D46:D51)</f>
-        <v>861115.06</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="36" t="s">
+      <c r="B50" s="152"/>
+      <c r="C50" s="152"/>
+      <c r="D50" s="181"/>
+      <c r="E50" s="151">
+        <f>SUM(D44:D49)</f>
+        <v>851115.06</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B53" s="154"/>
-      <c r="C53" s="154"/>
-      <c r="D53" s="182"/>
-      <c r="E53" s="155"/>
-    </row>
-    <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="152"/>
+      <c r="C51" s="152"/>
+      <c r="D51" s="179"/>
+      <c r="E51" s="153"/>
+    </row>
+    <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="164">
+        <v>52825.87</v>
+      </c>
+      <c r="E52" s="161" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" s="164"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="164">
+        <v>23726.77</v>
+      </c>
+      <c r="E53" s="161" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="166">
-        <v>52825.87</v>
-      </c>
-      <c r="E54" s="163" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
+      <c r="D54" s="164">
+        <v>27113.49</v>
+      </c>
+      <c r="E54" s="161" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="187" t="s">
+        <v>80</v>
+      </c>
+      <c r="B55" s="188"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="164">
+        <v>355815.42</v>
+      </c>
+      <c r="E55" s="161" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="182"/>
+      <c r="E56" s="151">
+        <f>SUM(D52:D55)</f>
+        <v>459481.55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="36"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="175"/>
+      <c r="E57" s="154"/>
+    </row>
+    <row r="58" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="166" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" s="159"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="164">
+        <v>54500</v>
+      </c>
+      <c r="E58" s="165" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="189" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" s="190"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="164">
+        <v>34000</v>
+      </c>
+      <c r="E59" s="165" t="s">
+        <v>104</v>
+      </c>
+      <c r="H59" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="187"/>
+      <c r="B60" s="188"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="186"/>
+      <c r="I60" s="187"/>
+      <c r="J60" s="188"/>
+    </row>
+    <row r="61" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="36"/>
+      <c r="C61" s="36"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="155">
+        <f>SUM(D58:D60)</f>
+        <v>88500</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="69"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="172"/>
+      <c r="E62" s="154"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="164">
+        <v>53000</v>
+      </c>
+      <c r="E63" s="156"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="164">
+        <v>46522.14</v>
+      </c>
+      <c r="E64" s="41"/>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65" s="53"/>
+      <c r="C65" s="53"/>
+      <c r="D65" s="112"/>
+      <c r="E65" s="106">
+        <f>SUM(D63:D64)</f>
+        <v>99522.14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="105"/>
+      <c r="E66" s="113"/>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="114"/>
+      <c r="E67" s="115">
+        <f>3500000-2553464.75</f>
+        <v>946535.25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1"/>
+      <c r="D68" s="116"/>
+      <c r="E68" s="117"/>
+      <c r="F68" s="45"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" s="10"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="118"/>
+      <c r="E69" s="119">
+        <f>(SUM(E27:E67))</f>
+        <v>3500000</v>
+      </c>
+      <c r="F69" s="143"/>
+      <c r="G69" s="45"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D70" s="116"/>
+      <c r="E70" s="116"/>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D71" s="116"/>
+      <c r="E71" s="116"/>
+      <c r="H71" s="183"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="120"/>
+      <c r="E72" s="121"/>
+    </row>
+    <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="187"/>
+      <c r="B73" s="188"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="131"/>
+      <c r="E73" s="107"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="187"/>
+      <c r="B74" s="188"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="109"/>
+      <c r="E74" s="107"/>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="189"/>
+      <c r="B75" s="190"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="109"/>
+      <c r="E75" s="107"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="108"/>
+      <c r="B76" s="110"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="109"/>
+      <c r="E76" s="107"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="51"/>
+      <c r="B77" s="50"/>
+      <c r="C77" s="50"/>
+      <c r="D77" s="60"/>
+      <c r="E77" s="60">
+        <f>SUM(D73:D76)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B80" s="31"/>
+      <c r="C80" s="31"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="104"/>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B82" s="10"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="70">
+        <f>E77+E80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="102" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" s="103">
+        <f>E69</f>
+        <v>3500000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" s="103">
+        <f>E69-E67</f>
+        <v>2553464.75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="102" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="103">
+        <f>E82-E80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="102" t="s">
+        <v>43</v>
+      </c>
+      <c r="B87" s="103">
+        <f>E82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="195"/>
+      <c r="B90" s="195"/>
+      <c r="C90" s="195"/>
+      <c r="D90" s="195"/>
+      <c r="E90" s="195"/>
+    </row>
+    <row r="91" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="195"/>
+      <c r="B91" s="195"/>
+      <c r="C91" s="195"/>
+      <c r="D91" s="195"/>
+      <c r="E91" s="195"/>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="195"/>
+      <c r="B92" s="195"/>
+      <c r="C92" s="195"/>
+      <c r="D92" s="195"/>
+      <c r="E92" s="195"/>
+    </row>
+    <row r="94" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B94" s="128"/>
+      <c r="C94" s="24"/>
+    </row>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="34"/>
+      <c r="B95" s="61">
+        <v>0</v>
+      </c>
+      <c r="C95" s="26"/>
+    </row>
+    <row r="96" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B96" s="41">
+        <f>PRORRATEO!F29</f>
+        <v>3065070.3000000007</v>
+      </c>
+      <c r="C96" s="24"/>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="25"/>
+      <c r="B97" s="41">
+        <v>0</v>
+      </c>
+      <c r="C97" s="24"/>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B98" s="111">
+        <f>B120</f>
+        <v>0</v>
+      </c>
+      <c r="C98" s="24"/>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="28"/>
+      <c r="B99" s="49"/>
+      <c r="C99" s="24"/>
+    </row>
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="126" t="s">
+        <v>49</v>
+      </c>
+      <c r="B100" s="49"/>
+      <c r="C100" s="24"/>
+    </row>
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101" s="49">
+        <f>-B85</f>
+        <v>-2553464.75</v>
+      </c>
+      <c r="C101" s="24"/>
+    </row>
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B102" s="49">
+        <f>-(B86)</f>
+        <v>0</v>
+      </c>
+      <c r="C102" s="24"/>
+    </row>
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B103" s="61">
+        <f>SUM(B95:B102)</f>
+        <v>511605.55000000075</v>
+      </c>
+      <c r="C103" s="27"/>
+      <c r="D103" s="45"/>
+    </row>
+    <row r="104" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="42"/>
+      <c r="C104" s="27"/>
+      <c r="D104" s="45"/>
+      <c r="E104" s="129"/>
+      <c r="F104" s="130"/>
+    </row>
+    <row r="105" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="43"/>
+      <c r="C105" s="27"/>
+    </row>
+    <row r="106" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106"/>
+      <c r="B106" s="42"/>
+      <c r="C106" s="38"/>
+    </row>
+    <row r="107" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="134" t="s">
+        <v>91</v>
+      </c>
+      <c r="B107" s="135">
+        <v>-726690.58609999763</v>
+      </c>
+      <c r="C107" s="38"/>
+      <c r="D107" s="48"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="B108" s="140">
+        <f>-B85</f>
+        <v>-2553464.75</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B109" s="140">
+        <f>-B86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="B55" s="166"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="193">
-        <v>23726.77</v>
-      </c>
-      <c r="E55" s="163" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="193">
-        <v>27113.49</v>
-      </c>
-      <c r="E56" s="163" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="195" t="s">
-        <v>82</v>
-      </c>
-      <c r="B57" s="196"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="166">
-        <v>355815.42</v>
-      </c>
-      <c r="E57" s="163" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="185"/>
-      <c r="E58" s="153">
-        <f>SUM(D54:D57)</f>
-        <v>459481.55</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="36"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="178"/>
-      <c r="E59" s="156"/>
-    </row>
-    <row r="60" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="169" t="s">
-        <v>122</v>
-      </c>
-      <c r="B60" s="161"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="166">
-        <v>54500</v>
-      </c>
-      <c r="E60" s="167" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="197" t="s">
-        <v>106</v>
-      </c>
-      <c r="B61" s="198"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="166">
-        <v>129500</v>
-      </c>
-      <c r="E61" s="167" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="187" t="s">
-        <v>96</v>
-      </c>
-      <c r="B62" s="188"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="110">
-        <v>59450</v>
-      </c>
-      <c r="E62" s="168" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="197" t="s">
-        <v>112</v>
-      </c>
-      <c r="B63" s="198"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="110">
-        <v>44480.41</v>
-      </c>
-      <c r="E63" s="167" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="197" t="s">
-        <v>112</v>
-      </c>
-      <c r="B64" s="198"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="110">
-        <v>9580</v>
-      </c>
-      <c r="E64" s="167" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="197" t="s">
-        <v>97</v>
-      </c>
-      <c r="B65" s="198"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="110">
-        <v>35000</v>
-      </c>
-      <c r="E65" s="168" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="195" t="s">
-        <v>119</v>
-      </c>
-      <c r="B66" s="196"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="110">
-        <v>85000</v>
-      </c>
-      <c r="E66" s="191" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="195" t="s">
-        <v>120</v>
-      </c>
-      <c r="B67" s="196"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="110">
-        <v>250000</v>
-      </c>
-      <c r="E67" s="191" t="s">
-        <v>102</v>
-      </c>
-      <c r="I67" s="195"/>
-      <c r="J67" s="196"/>
-    </row>
-    <row r="68" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="30" t="s">
+      <c r="B110" s="140">
+        <f>B120</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B111" s="141">
+        <f>PRORRATEO!F29</f>
+        <v>3065070.3000000007</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="142" t="s">
+        <v>57</v>
+      </c>
+      <c r="B112" s="184"/>
+    </row>
+    <row r="113" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="138" t="s">
+        <v>51</v>
+      </c>
+      <c r="B113" s="139">
+        <f>SUM(B107:C112)</f>
+        <v>-215085.03609999688</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="136"/>
+      <c r="B114" s="136"/>
+    </row>
+    <row r="115" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="196" t="s">
+        <v>33</v>
+      </c>
+      <c r="B116" s="196"/>
+      <c r="C116" s="196"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="196"/>
+      <c r="B117" s="196"/>
+      <c r="C117" s="196"/>
+    </row>
+    <row r="118" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="123"/>
+      <c r="B118" s="37"/>
+      <c r="C118" s="37">
+        <v>40000</v>
+      </c>
+      <c r="E118" s="143"/>
+    </row>
+    <row r="119" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="123"/>
+      <c r="B119" s="125"/>
+      <c r="C119" s="122"/>
+      <c r="D119" s="143"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="35"/>
-      <c r="E68" s="157">
-        <f>SUM(D60:D67)</f>
-        <v>667510.41</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="B69" s="69"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="175"/>
-      <c r="E69" s="156"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="166">
-        <v>53000</v>
-      </c>
-      <c r="E70" s="158"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="166">
-        <v>53598.95</v>
-      </c>
-      <c r="E71" s="41"/>
-    </row>
-    <row r="72" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="B72" s="53"/>
-      <c r="C72" s="53"/>
-      <c r="D72" s="113"/>
-      <c r="E72" s="107">
-        <f>SUM(D70:D71)</f>
-        <v>106598.95</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="5"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="106"/>
-      <c r="E73" s="114"/>
-    </row>
-    <row r="74" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B74" s="31"/>
-      <c r="C74" s="31"/>
-      <c r="D74" s="115"/>
-      <c r="E74" s="116"/>
-    </row>
-    <row r="75" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="1"/>
-      <c r="D75" s="117"/>
-      <c r="E75" s="118"/>
-      <c r="F75" s="45"/>
-    </row>
-    <row r="76" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B76" s="10"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="119"/>
-      <c r="E76" s="120">
-        <f>(SUM(E29:E74))</f>
-        <v>3471798.97</v>
-      </c>
-      <c r="F76" s="144"/>
-      <c r="G76" s="45"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D77" s="117"/>
-      <c r="E77" s="117"/>
-    </row>
-    <row r="78" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D78" s="117"/>
-      <c r="E78" s="117"/>
-      <c r="H78" s="186"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B79" s="12"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="121"/>
-      <c r="E79" s="122"/>
-    </row>
-    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="195"/>
-      <c r="B80" s="196"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="132"/>
-      <c r="E80" s="108"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="195"/>
-      <c r="B81" s="196"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="110"/>
-      <c r="E81" s="108"/>
-    </row>
-    <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="197"/>
-      <c r="B82" s="198"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="110"/>
-      <c r="E82" s="108"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="109"/>
-      <c r="B83" s="111"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="110"/>
-      <c r="E83" s="108"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="51"/>
-      <c r="B84" s="50"/>
-      <c r="C84" s="50"/>
-      <c r="D84" s="60"/>
-      <c r="E84" s="60">
-        <f>SUM(D80:D83)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="32"/>
-      <c r="E87" s="105"/>
-    </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B89" s="10"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="70">
-        <f>E84+E87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="91" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="103" t="s">
-        <v>14</v>
-      </c>
-      <c r="B91" s="104">
-        <f>E76</f>
-        <v>3471798.97</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" s="104">
-        <f>E76-E74</f>
-        <v>3471798.97</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="103" t="s">
-        <v>22</v>
-      </c>
-      <c r="B93" s="104">
-        <f>E89-E87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="103" t="s">
-        <v>45</v>
-      </c>
-      <c r="B94" s="104">
-        <f>E89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="203"/>
-      <c r="B97" s="203"/>
-      <c r="C97" s="203"/>
-      <c r="D97" s="203"/>
-      <c r="E97" s="203"/>
-    </row>
-    <row r="98" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="203"/>
-      <c r="B98" s="203"/>
-      <c r="C98" s="203"/>
-      <c r="D98" s="203"/>
-      <c r="E98" s="203"/>
-    </row>
-    <row r="99" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="203"/>
-      <c r="B99" s="203"/>
-      <c r="C99" s="203"/>
-      <c r="D99" s="203"/>
-      <c r="E99" s="203"/>
-    </row>
-    <row r="101" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B101" s="129"/>
-      <c r="C101" s="24"/>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="34"/>
-      <c r="B102" s="61">
-        <v>0</v>
-      </c>
-      <c r="C102" s="26"/>
-    </row>
-    <row r="103" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B103" s="41">
-        <f>PRORRATEO!F29</f>
-        <v>3025933.6900000009</v>
-      </c>
-      <c r="C103" s="24"/>
-    </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="25"/>
-      <c r="B104" s="41">
-        <v>0</v>
-      </c>
-      <c r="C104" s="24"/>
-    </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B105" s="112">
-        <f>B127</f>
-        <v>0</v>
-      </c>
-      <c r="C105" s="24"/>
-    </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="28"/>
-      <c r="B106" s="49"/>
-      <c r="C106" s="24"/>
-    </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="127" t="s">
-        <v>51</v>
-      </c>
-      <c r="B107" s="49"/>
-      <c r="C107" s="24"/>
-    </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B108" s="49">
-        <f>-B92</f>
-        <v>-3471798.97</v>
-      </c>
-      <c r="C108" s="24"/>
-    </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B109" s="49">
-        <f>-(B93)</f>
-        <v>0</v>
-      </c>
-      <c r="C109" s="24"/>
-    </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="B110" s="61">
-        <f>SUM(B102:B109)</f>
-        <v>-445865.27999999933</v>
-      </c>
-      <c r="C110" s="27"/>
-      <c r="D110" s="45"/>
-    </row>
-    <row r="111" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B111" s="42"/>
-      <c r="C111" s="27"/>
-      <c r="D111" s="45"/>
-      <c r="E111" s="130"/>
-      <c r="F111" s="131"/>
-    </row>
-    <row r="112" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="43"/>
-      <c r="C112" s="27"/>
-    </row>
-    <row r="113" spans="1:13" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113"/>
-      <c r="B113" s="42"/>
-      <c r="C113" s="38"/>
-    </row>
-    <row r="114" spans="1:13" s="39" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="135" t="s">
-        <v>95</v>
-      </c>
-      <c r="B114" s="136">
-        <v>-87279.01609999832</v>
-      </c>
-      <c r="C114" s="38"/>
-      <c r="D114" s="48"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="B115" s="141">
-        <f>-B92</f>
-        <v>-3471798.97</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="B116" s="141">
-        <f>-B93</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A117" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="B117" s="141">
-        <f>B127</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A118" s="56" t="s">
-        <v>58</v>
-      </c>
-      <c r="B118" s="142">
-        <f>PRORRATEO!F29</f>
-        <v>3025933.6900000009</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="143" t="s">
-        <v>59</v>
-      </c>
-      <c r="B119" s="189"/>
-    </row>
-    <row r="120" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="139" t="s">
-        <v>53</v>
-      </c>
-      <c r="B120" s="140">
-        <f>SUM(B114:C119)</f>
-        <v>-533144.29609999759</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="137"/>
-      <c r="B121" s="137"/>
-    </row>
-    <row r="122" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="204" t="s">
-        <v>34</v>
-      </c>
-      <c r="B123" s="204"/>
-      <c r="C123" s="204"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="204"/>
-      <c r="B124" s="204"/>
-      <c r="C124" s="204"/>
-    </row>
-    <row r="125" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="124"/>
-      <c r="B125" s="37"/>
-      <c r="C125" s="37">
-        <v>40000</v>
-      </c>
-      <c r="E125" s="144"/>
-    </row>
-    <row r="126" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="124"/>
-      <c r="B126" s="126"/>
-      <c r="C126" s="123"/>
-      <c r="D126" s="144"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A127" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="B127" s="125">
-        <f>SUM(B125:B126)</f>
-        <v>0</v>
-      </c>
-      <c r="C127" s="47"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M128" s="8"/>
-    </row>
-    <row r="129" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="203"/>
-      <c r="B129" s="203"/>
-      <c r="C129" s="203"/>
-      <c r="D129" s="203"/>
-      <c r="E129" s="203"/>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" s="203"/>
-      <c r="B130" s="203"/>
-      <c r="C130" s="203"/>
-      <c r="D130" s="203"/>
-      <c r="E130" s="203"/>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="203"/>
-      <c r="B131" s="203"/>
-      <c r="C131" s="203"/>
-      <c r="D131" s="203"/>
-      <c r="E131" s="203"/>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" s="203"/>
-      <c r="B132" s="203"/>
-      <c r="C132" s="203"/>
-      <c r="D132" s="203"/>
-      <c r="E132" s="203"/>
+      <c r="B120" s="124">
+        <f>SUM(B118:B119)</f>
+        <v>0</v>
+      </c>
+      <c r="C120" s="47"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M121" s="8"/>
+    </row>
+    <row r="122" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="195"/>
+      <c r="B122" s="195"/>
+      <c r="C122" s="195"/>
+      <c r="D122" s="195"/>
+      <c r="E122" s="195"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="195"/>
+      <c r="B123" s="195"/>
+      <c r="C123" s="195"/>
+      <c r="D123" s="195"/>
+      <c r="E123" s="195"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="195"/>
+      <c r="B124" s="195"/>
+      <c r="C124" s="195"/>
+      <c r="D124" s="195"/>
+      <c r="E124" s="195"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" s="195"/>
+      <c r="B125" s="195"/>
+      <c r="C125" s="195"/>
+      <c r="D125" s="195"/>
+      <c r="E125" s="195"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A129:E132"/>
-    <mergeCell ref="A123:C124"/>
-    <mergeCell ref="A97:E99"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A38:B38"/>
+  <mergeCells count="17">
+    <mergeCell ref="A122:E125"/>
+    <mergeCell ref="A116:C117"/>
+    <mergeCell ref="A90:E92"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2994,73 +2881,70 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="0.109375" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="0.44140625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" customWidth="1"/>
-    <col min="16" max="16" width="0.109375" customWidth="1"/>
-    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="0.140625" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="13" max="13" width="12" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="0.140625" customWidth="1"/>
+    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="205"/>
-      <c r="E1" s="205"/>
-      <c r="F1" s="205"/>
-      <c r="G1" s="205"/>
-      <c r="H1" s="205"/>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
-      <c r="K1" s="205"/>
-      <c r="L1" s="205"/>
-      <c r="M1" s="205"/>
+      <c r="D1" s="197"/>
+      <c r="E1" s="197"/>
+      <c r="F1" s="197"/>
+      <c r="G1" s="197"/>
+      <c r="H1" s="197"/>
+      <c r="I1" s="197"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="6"/>
       <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-    </row>
-    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="170">
+      <c r="F2" s="167">
         <v>86134.56</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="L2" s="6"/>
-      <c r="M2" s="134">
-        <v>3100000</v>
-      </c>
+      <c r="I2" s="7"/>
+      <c r="J2" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K2" s="6"/>
+      <c r="L2" s="133">
+        <v>3500000</v>
+      </c>
+      <c r="M2" s="57"/>
       <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="22"/>
-    </row>
-    <row r="3" spans="1:18" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O2" s="22"/>
+    </row>
+    <row r="3" spans="1:17" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3072,1114 +2956,1083 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
+      <c r="L3" s="58"/>
       <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="62"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="210" t="s">
+      <c r="N3" s="62"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="210" t="s">
+      <c r="B4" s="202" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="202" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="202" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="206" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="210" t="s">
+      <c r="E4" s="198" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="210" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="212" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="206" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" s="206" t="s">
+      <c r="G4" s="204" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="198" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="198" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="206" t="s">
+      <c r="J4" s="198" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="215" t="s">
-        <v>90</v>
-      </c>
-      <c r="M4" s="65" t="s">
-        <v>41</v>
-      </c>
-      <c r="N4" s="208" t="s">
+      <c r="K4" s="207" t="s">
+        <v>86</v>
+      </c>
+      <c r="L4" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="200" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="217" t="s">
-        <v>40</v>
-      </c>
-      <c r="R4" s="45"/>
-    </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="211"/>
-      <c r="B5" s="211"/>
-      <c r="C5" s="219"/>
-      <c r="D5" s="211"/>
-      <c r="E5" s="207"/>
-      <c r="F5" s="211"/>
-      <c r="G5" s="219"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="207"/>
-      <c r="J5" s="214"/>
-      <c r="K5" s="207"/>
-      <c r="L5" s="216"/>
-      <c r="M5" s="63" t="str">
+      <c r="N4" s="209" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4" s="45"/>
+    </row>
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="203"/>
+      <c r="B5" s="203"/>
+      <c r="C5" s="211"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="203"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="199"/>
+      <c r="I5" s="206"/>
+      <c r="J5" s="199"/>
+      <c r="K5" s="208"/>
+      <c r="L5" s="63" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/09</v>
       </c>
-      <c r="N5" s="209"/>
-      <c r="O5" s="218"/>
-    </row>
-    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="201"/>
+      <c r="N5" s="210"/>
+    </row>
+    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="66">
         <v>1</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C6" s="66"/>
       <c r="D6" s="75">
         <v>6.69</v>
       </c>
       <c r="E6" s="76">
-        <v>193082.01</v>
+        <v>213152.01</v>
       </c>
       <c r="F6" s="78">
         <f>E6</f>
-        <v>193082.01</v>
-      </c>
-      <c r="G6" s="78"/>
+        <v>213152.01</v>
+      </c>
+      <c r="G6" s="79">
+        <f t="shared" ref="G6:G23" si="0">E6-F6</f>
+        <v>0</v>
+      </c>
       <c r="H6" s="79">
-        <f>E6-F6</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="79">
-        <f>IF(H6&gt;0,H6*3%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="80">
-        <v>0</v>
-      </c>
-      <c r="K6" s="81">
-        <f>M$2*D6/100</f>
-        <v>207390</v>
-      </c>
-      <c r="L6" s="171">
-        <f>F$2*D6/100</f>
+        <f>IF(G6&gt;0,G6*3%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="80">
+        <v>0</v>
+      </c>
+      <c r="J6" s="81">
+        <f>L$2*D6/100</f>
+        <v>234150</v>
+      </c>
+      <c r="K6" s="168">
+        <f t="shared" ref="K6:K23" si="1">F$2*D6/100</f>
         <v>5762.4020639999999</v>
       </c>
-      <c r="M6" s="83">
-        <f>ROUND(SUM(H6:L6),0) + P6</f>
-        <v>213152.01</v>
-      </c>
-      <c r="N6" s="84">
-        <f>ROUND(M6*6% + M6,0) + P6</f>
-        <v>225941.01</v>
-      </c>
-      <c r="O6" s="85">
-        <f>ROUND(M6*3%,0) + M6</f>
-        <v>219547.01</v>
-      </c>
-      <c r="P6" s="45">
+      <c r="L6" s="83">
+        <f>ROUND(SUM(G6:K6),0) + O6</f>
+        <v>239912.01</v>
+      </c>
+      <c r="M6" s="84">
+        <f>ROUND(L6*6% + L6,0) + O6</f>
+        <v>254307.01</v>
+      </c>
+      <c r="N6" s="85">
+        <f>ROUND(L6*3%,0) + L6</f>
+        <v>247109.01</v>
+      </c>
+      <c r="O6" s="45">
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="66">
         <f>A6+1</f>
         <v>2</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" s="67"/>
       <c r="D7" s="75">
         <v>5.88</v>
       </c>
       <c r="E7" s="76">
-        <v>223221.02</v>
+        <v>365762.02</v>
       </c>
       <c r="F7" s="78">
-        <v>50000</v>
-      </c>
-      <c r="G7" s="78"/>
+        <f>150000+100000</f>
+        <v>250000</v>
+      </c>
+      <c r="G7" s="79">
+        <f t="shared" si="0"/>
+        <v>115762.02000000002</v>
+      </c>
       <c r="H7" s="79">
-        <f t="shared" ref="H7:H23" si="0">E7-F7</f>
-        <v>173221.02</v>
-      </c>
-      <c r="I7" s="79">
-        <f t="shared" ref="I7:I23" si="1">IF(H7&gt;0,H7*3%,0)</f>
-        <v>5196.6305999999995</v>
-      </c>
-      <c r="J7" s="80">
-        <v>0</v>
-      </c>
-      <c r="K7" s="81">
-        <f t="shared" ref="K7:K23" si="2">M$2*D7%</f>
-        <v>182280</v>
-      </c>
-      <c r="L7" s="171">
-        <f t="shared" ref="L7:L23" si="3">F$2*D7/100</f>
+        <f t="shared" ref="H7:H23" si="2">IF(G7&gt;0,G7*3%,0)</f>
+        <v>3472.8606000000004</v>
+      </c>
+      <c r="I7" s="80">
+        <v>0</v>
+      </c>
+      <c r="J7" s="81">
+        <f t="shared" ref="J7:J23" si="3">L$2*D7%</f>
+        <v>205800</v>
+      </c>
+      <c r="K7" s="168">
+        <f t="shared" si="1"/>
         <v>5064.7121280000001</v>
       </c>
-      <c r="M7" s="83">
-        <f t="shared" ref="M7:M23" si="4">ROUND(SUM(H7:L7),0) + P7</f>
-        <v>365762.02</v>
-      </c>
-      <c r="N7" s="84">
-        <f t="shared" ref="N7:N23" si="5">ROUND(M7*6% + M7,0) + P7</f>
-        <v>387708.02</v>
-      </c>
-      <c r="O7" s="85">
-        <f t="shared" ref="O7:O23" si="6">ROUND(M7*3%,0) + M7</f>
-        <v>376735.02</v>
-      </c>
-      <c r="P7" s="45">
-        <f>P6+0.01</f>
+      <c r="L7" s="83">
+        <f t="shared" ref="L7:L23" si="4">ROUND(SUM(G7:K7),0) + O7</f>
+        <v>330100.02</v>
+      </c>
+      <c r="M7" s="84">
+        <f t="shared" ref="M7:M23" si="5">ROUND(L7*6% + L7,0) + O7</f>
+        <v>349906.02</v>
+      </c>
+      <c r="N7" s="85">
+        <f t="shared" ref="N7:N23" si="6">ROUND(L7*3%,0) + L7</f>
+        <v>340003.02</v>
+      </c>
+      <c r="O7" s="45">
+        <f>O6+0.01</f>
         <v>0.02</v>
       </c>
-      <c r="Q7" s="45"/>
-    </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P7" s="45"/>
+    </row>
+    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="66">
         <f t="shared" ref="A8:A23" si="7">A7+1</f>
         <v>3</v>
       </c>
       <c r="B8" s="66" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C8" s="67"/>
       <c r="D8" s="75">
         <v>6.65</v>
       </c>
       <c r="E8" s="76">
-        <v>212852.03</v>
+        <v>211878.03</v>
       </c>
       <c r="F8" s="78">
         <f>E8</f>
-        <v>212852.03</v>
-      </c>
-      <c r="G8" s="78"/>
+        <v>211878.03</v>
+      </c>
+      <c r="G8" s="79">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H8" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="80">
+        <v>0</v>
+      </c>
+      <c r="J8" s="81">
+        <f t="shared" si="3"/>
+        <v>232750</v>
+      </c>
+      <c r="K8" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="80">
-        <v>0</v>
-      </c>
-      <c r="K8" s="81">
-        <f t="shared" si="2"/>
-        <v>206150</v>
-      </c>
-      <c r="L8" s="171">
-        <f t="shared" si="3"/>
         <v>5727.9482400000006</v>
       </c>
-      <c r="M8" s="83">
+      <c r="L8" s="83">
         <f t="shared" si="4"/>
-        <v>211878.03</v>
-      </c>
-      <c r="N8" s="84">
+        <v>238478.03</v>
+      </c>
+      <c r="M8" s="84">
         <f t="shared" si="5"/>
-        <v>224591.03</v>
-      </c>
-      <c r="O8" s="85">
+        <v>252787.03</v>
+      </c>
+      <c r="N8" s="85">
         <f t="shared" si="6"/>
-        <v>218234.03</v>
-      </c>
-      <c r="P8" s="45">
-        <f t="shared" ref="P8:P24" si="8">P7+0.01</f>
+        <v>245632.03</v>
+      </c>
+      <c r="O8" s="45">
+        <f t="shared" ref="O8:O24" si="8">O7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="66">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C9" s="67"/>
       <c r="D9" s="75">
         <v>6.73</v>
       </c>
       <c r="E9" s="76">
-        <v>194237.04</v>
+        <v>214427.04</v>
       </c>
       <c r="F9" s="78">
         <f t="shared" ref="F9:F23" si="9">E9</f>
-        <v>194237.04</v>
-      </c>
-      <c r="G9" s="78"/>
+        <v>214427.04</v>
+      </c>
+      <c r="G9" s="79">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H9" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="80">
+        <v>0</v>
+      </c>
+      <c r="J9" s="81">
+        <f t="shared" si="3"/>
+        <v>235550</v>
+      </c>
+      <c r="K9" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="80">
-        <v>0</v>
-      </c>
-      <c r="K9" s="81">
-        <f t="shared" si="2"/>
-        <v>208630</v>
-      </c>
-      <c r="L9" s="171">
-        <f t="shared" si="3"/>
         <v>5796.855888</v>
       </c>
-      <c r="M9" s="83">
+      <c r="L9" s="83">
         <f t="shared" si="4"/>
-        <v>214427.04</v>
-      </c>
-      <c r="N9" s="84">
+        <v>241347.04</v>
+      </c>
+      <c r="M9" s="84">
         <f t="shared" si="5"/>
-        <v>227293.04</v>
-      </c>
-      <c r="O9" s="85">
+        <v>255828.04</v>
+      </c>
+      <c r="N9" s="85">
         <f t="shared" si="6"/>
-        <v>220860.04</v>
-      </c>
-      <c r="P9" s="45">
+        <v>248587.04</v>
+      </c>
+      <c r="O9" s="45">
         <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
-      <c r="R9" s="45"/>
-    </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q9" s="45"/>
+    </row>
+    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="66">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C10" s="67"/>
       <c r="D10" s="75">
         <v>8.0399999999999991</v>
       </c>
       <c r="E10" s="76">
-        <v>439935.05</v>
+        <v>263850.05</v>
       </c>
       <c r="F10" s="78">
         <f>E10</f>
-        <v>439935.05</v>
-      </c>
-      <c r="G10" s="78"/>
+        <v>263850.05</v>
+      </c>
+      <c r="G10" s="79">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H10" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="80">
+        <v>0</v>
+      </c>
+      <c r="J10" s="81">
+        <f t="shared" si="3"/>
+        <v>281399.99999999994</v>
+      </c>
+      <c r="K10" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="80">
-        <v>0</v>
-      </c>
-      <c r="K10" s="81">
-        <f t="shared" si="2"/>
-        <v>249239.99999999994</v>
-      </c>
-      <c r="L10" s="171">
-        <f t="shared" si="3"/>
         <v>6925.2186239999983</v>
       </c>
-      <c r="M10" s="83">
+      <c r="L10" s="83">
         <f t="shared" si="4"/>
-        <v>256165.05</v>
-      </c>
-      <c r="N10" s="84">
+        <v>288325.05</v>
+      </c>
+      <c r="M10" s="84">
         <f t="shared" si="5"/>
-        <v>271535.05</v>
-      </c>
-      <c r="O10" s="85">
+        <v>305625.05</v>
+      </c>
+      <c r="N10" s="85">
         <f t="shared" si="6"/>
-        <v>263850.05</v>
-      </c>
-      <c r="P10" s="45">
+        <v>296975.05</v>
+      </c>
+      <c r="O10" s="45">
         <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
-      <c r="R10" s="45"/>
-    </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q10" s="45"/>
+    </row>
+    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="66">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C11" s="66"/>
       <c r="D11" s="75">
         <v>4.7300000000000004</v>
       </c>
       <c r="E11" s="76">
-        <v>136514.06</v>
+        <v>150704.06</v>
       </c>
       <c r="F11" s="78">
         <f t="shared" si="9"/>
-        <v>136514.06</v>
-      </c>
-      <c r="G11" s="78"/>
+        <v>150704.06</v>
+      </c>
+      <c r="G11" s="79">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H11" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="80">
+        <v>0</v>
+      </c>
+      <c r="J11" s="81">
+        <f t="shared" si="3"/>
+        <v>165550</v>
+      </c>
+      <c r="K11" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="80">
-        <v>0</v>
-      </c>
-      <c r="K11" s="81">
-        <f t="shared" si="2"/>
-        <v>146630</v>
-      </c>
-      <c r="L11" s="171">
-        <f t="shared" si="3"/>
         <v>4074.1646880000003</v>
       </c>
-      <c r="M11" s="83">
+      <c r="L11" s="83">
         <f t="shared" si="4"/>
-        <v>150704.06</v>
-      </c>
-      <c r="N11" s="84">
+        <v>169624.06</v>
+      </c>
+      <c r="M11" s="84">
         <f t="shared" si="5"/>
-        <v>159746.06</v>
-      </c>
-      <c r="O11" s="85">
+        <v>179802.06</v>
+      </c>
+      <c r="N11" s="85">
         <f t="shared" si="6"/>
-        <v>155225.06</v>
-      </c>
-      <c r="P11" s="45">
+        <v>174713.06</v>
+      </c>
+      <c r="O11" s="45">
         <f t="shared" si="8"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="66">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="B12" s="66" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C12" s="66"/>
       <c r="D12" s="75">
         <v>5.67</v>
       </c>
       <c r="E12" s="76">
-        <v>163644.07</v>
+        <v>180654.07</v>
       </c>
       <c r="F12" s="78">
         <f>E12</f>
-        <v>163644.07</v>
-      </c>
-      <c r="G12" s="78"/>
+        <v>180654.07</v>
+      </c>
+      <c r="G12" s="79">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H12" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="80">
+        <v>0</v>
+      </c>
+      <c r="J12" s="81">
+        <f t="shared" si="3"/>
+        <v>198450</v>
+      </c>
+      <c r="K12" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="80">
-        <v>0</v>
-      </c>
-      <c r="K12" s="81">
-        <f t="shared" si="2"/>
-        <v>175770</v>
-      </c>
-      <c r="L12" s="171">
-        <f t="shared" si="3"/>
         <v>4883.8295519999992</v>
       </c>
-      <c r="M12" s="83">
+      <c r="L12" s="83">
         <f t="shared" si="4"/>
-        <v>180654.07</v>
-      </c>
-      <c r="N12" s="84">
+        <v>203334.07</v>
+      </c>
+      <c r="M12" s="84">
         <f t="shared" si="5"/>
-        <v>191493.07</v>
-      </c>
-      <c r="O12" s="85">
+        <v>215534.07</v>
+      </c>
+      <c r="N12" s="85">
         <f t="shared" si="6"/>
-        <v>186074.07</v>
-      </c>
-      <c r="P12" s="45">
+        <v>209434.07</v>
+      </c>
+      <c r="O12" s="45">
         <f t="shared" si="8"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="66">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" s="67"/>
       <c r="D13" s="75">
         <v>5.67</v>
       </c>
       <c r="E13" s="76">
-        <v>168553.08</v>
+        <v>180654.07999999999</v>
       </c>
       <c r="F13" s="78">
-        <f>E13</f>
-        <v>168553.08</v>
-      </c>
-      <c r="G13" s="78"/>
+        <f>100000+80000</f>
+        <v>180000</v>
+      </c>
+      <c r="G13" s="79">
+        <f t="shared" si="0"/>
+        <v>654.07999999998719</v>
+      </c>
       <c r="H13" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="79">
+        <f t="shared" si="2"/>
+        <v>19.622399999999615</v>
+      </c>
+      <c r="I13" s="80">
+        <v>0</v>
+      </c>
+      <c r="J13" s="81">
+        <f t="shared" si="3"/>
+        <v>198450</v>
+      </c>
+      <c r="K13" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="80">
-        <v>0</v>
-      </c>
-      <c r="K13" s="81">
-        <f t="shared" si="2"/>
-        <v>175770</v>
-      </c>
-      <c r="L13" s="171">
-        <f t="shared" si="3"/>
         <v>4883.8295519999992</v>
       </c>
-      <c r="M13" s="83">
+      <c r="L13" s="83">
         <f t="shared" si="4"/>
-        <v>180654.07999999999</v>
-      </c>
-      <c r="N13" s="84">
+        <v>204008.08</v>
+      </c>
+      <c r="M13" s="84">
         <f t="shared" si="5"/>
-        <v>191493.08</v>
-      </c>
-      <c r="O13" s="85">
+        <v>216249.08</v>
+      </c>
+      <c r="N13" s="85">
         <f t="shared" si="6"/>
-        <v>186074.08</v>
-      </c>
-      <c r="P13" s="45">
+        <v>210128.08</v>
+      </c>
+      <c r="O13" s="45">
         <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
-      <c r="R13" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="66">
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="B14" s="66" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C14" s="67"/>
       <c r="D14" s="75">
         <v>7.67</v>
       </c>
       <c r="E14" s="76">
-        <v>221367.09</v>
+        <v>244377.09</v>
       </c>
       <c r="F14" s="78">
         <f t="shared" si="9"/>
-        <v>221367.09</v>
-      </c>
-      <c r="G14" s="78"/>
+        <v>244377.09</v>
+      </c>
+      <c r="G14" s="79">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H14" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="80">
+        <v>0</v>
+      </c>
+      <c r="J14" s="81">
+        <f t="shared" si="3"/>
+        <v>268450</v>
+      </c>
+      <c r="K14" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="80">
-        <v>0</v>
-      </c>
-      <c r="K14" s="81">
-        <f t="shared" si="2"/>
-        <v>237770</v>
-      </c>
-      <c r="L14" s="171">
-        <f t="shared" si="3"/>
         <v>6606.5207519999994</v>
       </c>
-      <c r="M14" s="83">
+      <c r="L14" s="83">
         <f t="shared" si="4"/>
-        <v>244377.09</v>
-      </c>
-      <c r="N14" s="84">
+        <v>275057.09000000003</v>
+      </c>
+      <c r="M14" s="84">
         <f t="shared" si="5"/>
-        <v>259040.09</v>
-      </c>
-      <c r="O14" s="85">
+        <v>291561.09000000003</v>
+      </c>
+      <c r="N14" s="85">
         <f t="shared" si="6"/>
-        <v>251708.09</v>
-      </c>
-      <c r="P14" s="45">
+        <v>283309.09000000003</v>
+      </c>
+      <c r="O14" s="45">
         <f t="shared" si="8"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="66">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="B15" s="66" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C15" s="67"/>
       <c r="D15" s="75">
         <v>4.9000000000000004</v>
       </c>
       <c r="E15" s="76">
-        <v>141421.1</v>
+        <v>160805.1</v>
       </c>
       <c r="F15" s="78">
-        <f t="shared" si="9"/>
-        <v>141421.1</v>
-      </c>
-      <c r="G15" s="78"/>
+        <v>151121.1</v>
+      </c>
+      <c r="G15" s="79">
+        <f t="shared" si="0"/>
+        <v>9684</v>
+      </c>
       <c r="H15" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="79">
+        <f t="shared" si="2"/>
+        <v>290.52</v>
+      </c>
+      <c r="I15" s="80">
+        <v>0</v>
+      </c>
+      <c r="J15" s="81">
+        <f t="shared" si="3"/>
+        <v>171500</v>
+      </c>
+      <c r="K15" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="80">
-        <v>0</v>
-      </c>
-      <c r="K15" s="81">
-        <f t="shared" si="2"/>
-        <v>151900</v>
-      </c>
-      <c r="L15" s="171">
-        <f t="shared" si="3"/>
         <v>4220.5934400000006</v>
       </c>
-      <c r="M15" s="83">
+      <c r="L15" s="83">
         <f t="shared" si="4"/>
-        <v>156121.1</v>
-      </c>
-      <c r="N15" s="84">
+        <v>185695.1</v>
+      </c>
+      <c r="M15" s="84">
         <f t="shared" si="5"/>
-        <v>165488.1</v>
-      </c>
-      <c r="O15" s="85">
+        <v>196837.1</v>
+      </c>
+      <c r="N15" s="85">
         <f t="shared" si="6"/>
-        <v>160805.1</v>
-      </c>
-      <c r="P15" s="45">
+        <v>191266.1</v>
+      </c>
+      <c r="O15" s="45">
         <f t="shared" si="8"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="66">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="B16" s="66" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C16" s="67"/>
       <c r="D16" s="75">
         <v>5.63</v>
       </c>
       <c r="E16" s="76">
-        <v>162489.10999999999</v>
+        <v>179379.11</v>
       </c>
       <c r="F16" s="78">
         <f t="shared" si="9"/>
-        <v>162489.10999999999</v>
-      </c>
-      <c r="G16" s="78"/>
+        <v>179379.11</v>
+      </c>
+      <c r="G16" s="79">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H16" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="80">
+        <v>0</v>
+      </c>
+      <c r="J16" s="81">
+        <f t="shared" si="3"/>
+        <v>197050</v>
+      </c>
+      <c r="K16" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="80">
-        <v>0</v>
-      </c>
-      <c r="K16" s="81">
-        <f t="shared" si="2"/>
-        <v>174530</v>
-      </c>
-      <c r="L16" s="171">
-        <f t="shared" si="3"/>
         <v>4849.375728</v>
       </c>
-      <c r="M16" s="83">
+      <c r="L16" s="83">
         <f t="shared" si="4"/>
-        <v>179379.11</v>
-      </c>
-      <c r="N16" s="84">
+        <v>201899.11</v>
+      </c>
+      <c r="M16" s="84">
         <f t="shared" si="5"/>
-        <v>190142.11</v>
-      </c>
-      <c r="O16" s="85">
+        <v>214013.11</v>
+      </c>
+      <c r="N16" s="85">
         <f t="shared" si="6"/>
-        <v>184760.11</v>
-      </c>
-      <c r="P16" s="45">
+        <v>207956.11</v>
+      </c>
+      <c r="O16" s="45">
         <f t="shared" si="8"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="66">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="B17" s="66" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C17" s="67"/>
       <c r="D17" s="75">
         <v>5.55</v>
       </c>
       <c r="E17" s="76">
-        <v>160180.12</v>
+        <v>176830.12</v>
       </c>
       <c r="F17" s="78">
         <f t="shared" si="9"/>
-        <v>160180.12</v>
-      </c>
-      <c r="G17" s="78"/>
+        <v>176830.12</v>
+      </c>
+      <c r="G17" s="79">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H17" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="80">
+        <v>0</v>
+      </c>
+      <c r="J17" s="81">
+        <f t="shared" si="3"/>
+        <v>194250</v>
+      </c>
+      <c r="K17" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="80">
-        <v>0</v>
-      </c>
-      <c r="K17" s="81">
-        <f t="shared" si="2"/>
-        <v>172050</v>
-      </c>
-      <c r="L17" s="171">
-        <f t="shared" si="3"/>
         <v>4780.4680799999996</v>
       </c>
-      <c r="M17" s="83">
+      <c r="L17" s="83">
         <f t="shared" si="4"/>
-        <v>176830.12</v>
-      </c>
-      <c r="N17" s="84">
+        <v>199030.12</v>
+      </c>
+      <c r="M17" s="84">
         <f t="shared" si="5"/>
-        <v>187440.12</v>
-      </c>
-      <c r="O17" s="85">
+        <v>210972.12</v>
+      </c>
+      <c r="N17" s="85">
         <f t="shared" si="6"/>
-        <v>182135.12</v>
-      </c>
-      <c r="P17" s="45">
+        <v>205001.12</v>
+      </c>
+      <c r="O17" s="45">
         <f t="shared" si="8"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="66">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="B18" s="66" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C18" s="67"/>
       <c r="D18" s="75">
         <v>11.06</v>
       </c>
       <c r="E18" s="76">
-        <v>329019.13</v>
+        <v>352386.13</v>
       </c>
       <c r="F18" s="78">
         <f>E18</f>
-        <v>329019.13</v>
-      </c>
-      <c r="G18" s="78"/>
+        <v>352386.13</v>
+      </c>
+      <c r="G18" s="79">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H18" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="80">
+        <v>0</v>
+      </c>
+      <c r="J18" s="81">
+        <f t="shared" si="3"/>
+        <v>387100</v>
+      </c>
+      <c r="K18" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="80">
-        <v>0</v>
-      </c>
-      <c r="K18" s="81">
-        <f t="shared" si="2"/>
-        <v>342860</v>
-      </c>
-      <c r="L18" s="171">
-        <f t="shared" si="3"/>
         <v>9526.4823360000009</v>
       </c>
-      <c r="M18" s="83">
+      <c r="L18" s="83">
         <f t="shared" si="4"/>
-        <v>352386.13</v>
-      </c>
-      <c r="N18" s="84">
+        <v>396626.13</v>
+      </c>
+      <c r="M18" s="84">
         <f t="shared" si="5"/>
-        <v>373529.13</v>
-      </c>
-      <c r="O18" s="85">
+        <v>420424.13</v>
+      </c>
+      <c r="N18" s="85">
         <f t="shared" si="6"/>
-        <v>362958.13</v>
-      </c>
-      <c r="P18" s="45">
+        <v>408525.13</v>
+      </c>
+      <c r="O18" s="45">
         <f t="shared" si="8"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="66">
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="B19" s="66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19" s="67"/>
       <c r="D19" s="75">
         <v>3.3</v>
       </c>
       <c r="E19" s="76">
-        <v>95242.14</v>
-      </c>
-      <c r="F19" s="78">
-        <f>E19+9580</f>
-        <v>104822.14</v>
-      </c>
-      <c r="G19" s="78"/>
+        <v>95562.14</v>
+      </c>
+      <c r="F19" s="78"/>
+      <c r="G19" s="79">
+        <f t="shared" si="0"/>
+        <v>95562.14</v>
+      </c>
       <c r="H19" s="79">
-        <f t="shared" si="0"/>
-        <v>-9580</v>
-      </c>
-      <c r="I19" s="79">
+        <f t="shared" si="2"/>
+        <v>2866.8642</v>
+      </c>
+      <c r="I19" s="80">
+        <v>0</v>
+      </c>
+      <c r="J19" s="81">
+        <f t="shared" si="3"/>
+        <v>115500</v>
+      </c>
+      <c r="K19" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="80">
-        <v>0</v>
-      </c>
-      <c r="K19" s="81">
-        <f t="shared" si="2"/>
-        <v>102300</v>
-      </c>
-      <c r="L19" s="171">
-        <f t="shared" si="3"/>
         <v>2842.4404799999993</v>
       </c>
-      <c r="M19" s="83">
+      <c r="L19" s="83">
         <f t="shared" si="4"/>
-        <v>95562.14</v>
-      </c>
-      <c r="N19" s="84">
+        <v>216771.14</v>
+      </c>
+      <c r="M19" s="84">
         <f t="shared" si="5"/>
-        <v>101296.14</v>
-      </c>
-      <c r="O19" s="85">
+        <v>229777.14</v>
+      </c>
+      <c r="N19" s="85">
         <f t="shared" si="6"/>
-        <v>98429.14</v>
-      </c>
-      <c r="P19" s="45">
+        <v>223274.14</v>
+      </c>
+      <c r="O19" s="45">
         <f t="shared" si="8"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="66">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="B20" s="66" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C20" s="67"/>
       <c r="D20" s="75">
         <v>1.8</v>
       </c>
       <c r="E20" s="76">
-        <v>51950.15</v>
+        <v>57350.15</v>
       </c>
       <c r="F20" s="78">
         <f>E20</f>
-        <v>51950.15</v>
-      </c>
-      <c r="G20" s="78"/>
+        <v>57350.15</v>
+      </c>
+      <c r="G20" s="79">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H20" s="79">
-        <f>E20-F20</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="80">
+        <v>0</v>
+      </c>
+      <c r="J20" s="81">
+        <f t="shared" si="3"/>
+        <v>63000.000000000007</v>
+      </c>
+      <c r="K20" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="80">
-        <v>0</v>
-      </c>
-      <c r="K20" s="81">
-        <f t="shared" si="2"/>
-        <v>55800.000000000007</v>
-      </c>
-      <c r="L20" s="171">
-        <f t="shared" si="3"/>
         <v>1550.4220800000001</v>
       </c>
-      <c r="M20" s="83">
+      <c r="L20" s="83">
         <f t="shared" si="4"/>
-        <v>57350.15</v>
-      </c>
-      <c r="N20" s="84">
+        <v>64550.15</v>
+      </c>
+      <c r="M20" s="84">
         <f t="shared" si="5"/>
-        <v>60791.15</v>
-      </c>
-      <c r="O20" s="85">
+        <v>68423.149999999994</v>
+      </c>
+      <c r="N20" s="85">
         <f t="shared" si="6"/>
-        <v>59071.15</v>
-      </c>
-      <c r="P20" s="45">
+        <v>66487.149999999994</v>
+      </c>
+      <c r="O20" s="45">
         <f t="shared" si="8"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="66">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="B21" s="66" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C21" s="66"/>
       <c r="D21" s="75">
         <v>3.22</v>
       </c>
       <c r="E21" s="76">
-        <v>92934.16</v>
+        <v>102594.16</v>
       </c>
       <c r="F21" s="78">
         <f>E21</f>
-        <v>92934.16</v>
-      </c>
-      <c r="G21" s="78"/>
+        <v>102594.16</v>
+      </c>
+      <c r="G21" s="79">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H21" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="80">
+        <v>0</v>
+      </c>
+      <c r="J21" s="81">
+        <f t="shared" si="3"/>
+        <v>112700</v>
+      </c>
+      <c r="K21" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="80">
-        <v>0</v>
-      </c>
-      <c r="K21" s="81">
-        <f t="shared" si="2"/>
-        <v>99820</v>
-      </c>
-      <c r="L21" s="171">
-        <f t="shared" si="3"/>
         <v>2773.5328319999999</v>
       </c>
-      <c r="M21" s="83">
+      <c r="L21" s="83">
         <f t="shared" si="4"/>
-        <v>102594.16</v>
-      </c>
-      <c r="N21" s="84">
+        <v>115474.16</v>
+      </c>
+      <c r="M21" s="84">
         <f t="shared" si="5"/>
-        <v>108750.16</v>
-      </c>
-      <c r="O21" s="85">
+        <v>122403.16</v>
+      </c>
+      <c r="N21" s="85">
         <f t="shared" si="6"/>
-        <v>105672.16</v>
-      </c>
-      <c r="P21" s="45">
+        <v>118938.16</v>
+      </c>
+      <c r="O21" s="45">
         <f t="shared" si="8"/>
         <v>0.16</v>
       </c>
-      <c r="R21" s="44"/>
-    </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q21" s="44"/>
+    </row>
+    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="66">
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="B22" s="66" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C22" s="67"/>
       <c r="D22" s="75">
         <v>2.61</v>
       </c>
       <c r="E22" s="77">
-        <v>79406.17</v>
-      </c>
-      <c r="F22" s="78">
-        <f>E22</f>
-        <v>79406.17</v>
-      </c>
-      <c r="G22" s="78"/>
+        <v>83158.17</v>
+      </c>
+      <c r="F22" s="78"/>
+      <c r="G22" s="79">
+        <f t="shared" si="0"/>
+        <v>83158.17</v>
+      </c>
       <c r="H22" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="79">
+        <f t="shared" si="2"/>
+        <v>2494.7450999999996</v>
+      </c>
+      <c r="I22" s="80">
+        <v>0</v>
+      </c>
+      <c r="J22" s="81">
+        <f t="shared" si="3"/>
+        <v>91350</v>
+      </c>
+      <c r="K22" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="80">
-        <v>0</v>
-      </c>
-      <c r="K22" s="81">
-        <f t="shared" si="2"/>
-        <v>80910</v>
-      </c>
-      <c r="L22" s="171">
-        <f t="shared" si="3"/>
         <v>2248.1120159999996</v>
       </c>
-      <c r="M22" s="83">
+      <c r="L22" s="83">
         <f t="shared" si="4"/>
-        <v>83158.17</v>
-      </c>
-      <c r="N22" s="84">
+        <v>179251.17</v>
+      </c>
+      <c r="M22" s="84">
         <f t="shared" si="5"/>
-        <v>88148.17</v>
-      </c>
-      <c r="O22" s="85">
+        <v>190006.17</v>
+      </c>
+      <c r="N22" s="85">
         <f t="shared" si="6"/>
-        <v>85653.17</v>
-      </c>
-      <c r="P22" s="45">
+        <v>184629.17</v>
+      </c>
+      <c r="O22" s="45">
         <f t="shared" si="8"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="66">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="B23" s="66" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="133"/>
+        <v>78</v>
+      </c>
+      <c r="C23" s="132"/>
       <c r="D23" s="75">
         <v>4.28</v>
       </c>
       <c r="E23" s="76">
-        <v>123527.18</v>
+        <v>136367.18</v>
       </c>
       <c r="F23" s="78">
         <f t="shared" si="9"/>
-        <v>123527.18</v>
-      </c>
-      <c r="G23" s="78"/>
+        <v>136367.18</v>
+      </c>
+      <c r="G23" s="79">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H23" s="79">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="80">
+        <v>0</v>
+      </c>
+      <c r="J23" s="81">
+        <f t="shared" si="3"/>
+        <v>149800.00000000003</v>
+      </c>
+      <c r="K23" s="168">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="80">
-        <v>0</v>
-      </c>
-      <c r="K23" s="81">
-        <f t="shared" si="2"/>
-        <v>132680.00000000003</v>
-      </c>
-      <c r="L23" s="171">
-        <f t="shared" si="3"/>
         <v>3686.5591680000002</v>
       </c>
-      <c r="M23" s="83">
+      <c r="L23" s="83">
         <f t="shared" si="4"/>
-        <v>136367.18</v>
-      </c>
-      <c r="N23" s="84">
+        <v>153487.18</v>
+      </c>
+      <c r="M23" s="84">
         <f t="shared" si="5"/>
-        <v>144549.18</v>
-      </c>
-      <c r="O23" s="85">
+        <v>162696.18</v>
+      </c>
+      <c r="N23" s="85">
         <f t="shared" si="6"/>
-        <v>140458.18</v>
-      </c>
-      <c r="P23" s="45">
+        <v>158092.18</v>
+      </c>
+      <c r="O23" s="45">
         <f t="shared" si="8"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="R23" s="145"/>
-    </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="66"/>
       <c r="B24" s="66"/>
       <c r="C24" s="67"/>
       <c r="D24" s="75"/>
       <c r="E24" s="76"/>
-      <c r="F24" s="159"/>
-      <c r="G24" s="78"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="79"/>
       <c r="H24" s="79"/>
-      <c r="I24" s="79"/>
-      <c r="J24" s="80"/>
-      <c r="K24" s="81"/>
-      <c r="L24" s="82"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="84"/>
-      <c r="O24" s="85"/>
-      <c r="P24" s="45">
+      <c r="I24" s="80"/>
+      <c r="J24" s="81"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="83"/>
+      <c r="M24" s="84"/>
+      <c r="N24" s="85"/>
+      <c r="O24" s="45">
         <f t="shared" si="8"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="86"/>
       <c r="B25" s="66"/>
       <c r="C25" s="67"/>
@@ -4187,17 +4040,16 @@
       <c r="E25" s="88"/>
       <c r="F25" s="89"/>
       <c r="G25" s="90"/>
-      <c r="H25" s="91"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="80"/>
+      <c r="H25" s="79"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="91"/>
       <c r="K25" s="92"/>
-      <c r="L25" s="93"/>
-      <c r="M25" s="83"/>
-      <c r="N25" s="84"/>
-      <c r="O25" s="85"/>
-      <c r="P25" s="45"/>
-    </row>
-    <row r="26" spans="1:18" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L25" s="83"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="85"/>
+      <c r="O25" s="45"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="86"/>
       <c r="B26" s="68"/>
       <c r="C26" s="67"/>
@@ -4205,17 +4057,16 @@
       <c r="E26" s="88"/>
       <c r="F26" s="89"/>
       <c r="G26" s="90"/>
-      <c r="H26" s="91"/>
-      <c r="I26" s="79"/>
-      <c r="J26" s="80"/>
+      <c r="H26" s="79"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="91"/>
       <c r="K26" s="92"/>
-      <c r="L26" s="93"/>
-      <c r="M26" s="83"/>
-      <c r="N26" s="84"/>
-      <c r="O26" s="85"/>
-      <c r="P26" s="45"/>
-    </row>
-    <row r="27" spans="1:18" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L26" s="83"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="85"/>
+      <c r="O26" s="45"/>
+    </row>
+    <row r="27" spans="1:17" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="87"/>
       <c r="B27" s="66"/>
       <c r="C27" s="67"/>
@@ -4223,197 +4074,184 @@
       <c r="E27" s="88"/>
       <c r="F27" s="89"/>
       <c r="G27" s="90"/>
-      <c r="H27" s="91"/>
-      <c r="I27" s="79"/>
-      <c r="J27" s="80"/>
+      <c r="H27" s="79"/>
+      <c r="I27" s="80"/>
+      <c r="J27" s="91"/>
       <c r="K27" s="92"/>
-      <c r="L27" s="93"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="84"/>
-      <c r="O27" s="85"/>
-      <c r="P27" s="45"/>
-    </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L27" s="83"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="85"/>
+      <c r="O27" s="45"/>
+    </row>
+    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="66"/>
-      <c r="B28" s="94"/>
-      <c r="C28" s="94"/>
+      <c r="B28" s="93"/>
+      <c r="C28" s="93"/>
       <c r="D28" s="75"/>
       <c r="E28" s="88"/>
       <c r="F28" s="89"/>
       <c r="G28" s="90"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="80"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="80"/>
+      <c r="J28" s="91"/>
       <c r="K28" s="92"/>
-      <c r="L28" s="93"/>
+      <c r="L28" s="94"/>
       <c r="M28" s="95"/>
       <c r="N28" s="96"/>
-      <c r="O28" s="97"/>
-      <c r="P28" s="45"/>
-    </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="98"/>
-      <c r="B29" s="99"/>
-      <c r="C29" s="99"/>
-      <c r="D29" s="100">
+      <c r="O28" s="45"/>
+    </row>
+    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="97"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="99">
         <f>SUM(D6:D28)</f>
         <v>100.08</v>
       </c>
       <c r="E29" s="55">
         <f>SUM(E6:E28)</f>
-        <v>3189574.7100000009</v>
+        <v>3369890.7100000004</v>
       </c>
       <c r="F29" s="64">
         <f>SUM(F6:F28)</f>
-        <v>3025933.6900000009</v>
-      </c>
-      <c r="G29" s="55">
-        <f t="shared" ref="G29:N29" si="10">SUM(G6:G28)</f>
-        <v>0</v>
+        <v>3065070.3000000007</v>
+      </c>
+      <c r="G29" s="64">
+        <f>SUM(G6:G28)</f>
+        <v>304820.40999999997</v>
       </c>
       <c r="H29" s="64">
-        <f>SUM(H6:H28)</f>
-        <v>163641.01999999999</v>
+        <f t="shared" ref="H29:M29" si="10">SUM(H6:H28)</f>
+        <v>9144.6123000000007</v>
       </c>
       <c r="I29" s="64">
         <f t="shared" si="10"/>
-        <v>5196.6305999999995</v>
-      </c>
-      <c r="J29" s="64">
+        <v>0</v>
+      </c>
+      <c r="J29" s="137">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="138">
-        <f t="shared" si="10"/>
-        <v>3102480</v>
-      </c>
-      <c r="L29" s="64">
+        <v>3502800</v>
+      </c>
+      <c r="K29" s="64">
         <f t="shared" si="10"/>
         <v>86203.467647999991</v>
       </c>
-      <c r="M29" s="101">
-        <f>SUM(M6:M23)</f>
-        <v>3357521.7100000004</v>
-      </c>
-      <c r="N29" s="101">
+      <c r="L29" s="100">
+        <f>SUM(L6:L23)</f>
+        <v>3902969.7100000004</v>
+      </c>
+      <c r="M29" s="100">
         <f t="shared" si="10"/>
-        <v>3558974.7100000004</v>
-      </c>
-      <c r="O29" s="101">
-        <f>SUM(O6:O28)</f>
-        <v>3458249.7100000004</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4137151.7100000004</v>
+      </c>
+      <c r="N29" s="100">
+        <f>SUM(N6:N28)</f>
+        <v>4020059.7100000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="52"/>
       <c r="C30" s="52"/>
     </row>
-    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="203" t="str">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="195" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="203"/>
-      <c r="D32" s="203"/>
-      <c r="E32" s="203"/>
-      <c r="F32" s="203"/>
-      <c r="G32" s="203"/>
-      <c r="H32" s="203"/>
-      <c r="I32" s="203"/>
-      <c r="J32" s="203"/>
-      <c r="K32" s="203"/>
-      <c r="L32" s="203"/>
-      <c r="M32" s="203"/>
-    </row>
-    <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="203"/>
-      <c r="C33" s="203"/>
-      <c r="D33" s="203"/>
-      <c r="E33" s="203"/>
-      <c r="F33" s="203"/>
-      <c r="G33" s="203"/>
-      <c r="H33" s="203"/>
-      <c r="I33" s="203"/>
-      <c r="J33" s="203"/>
-      <c r="K33" s="203"/>
-      <c r="L33" s="203"/>
-      <c r="M33" s="203"/>
-    </row>
-    <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="203"/>
-      <c r="C34" s="203"/>
-      <c r="D34" s="203"/>
-      <c r="E34" s="203"/>
-      <c r="F34" s="203"/>
-      <c r="G34" s="203"/>
-      <c r="H34" s="203"/>
-      <c r="I34" s="203"/>
-      <c r="J34" s="203"/>
-      <c r="K34" s="203"/>
-      <c r="L34" s="203"/>
-      <c r="M34" s="203"/>
-    </row>
-    <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="203"/>
-      <c r="C35" s="203"/>
-      <c r="D35" s="203"/>
-      <c r="E35" s="203"/>
-      <c r="F35" s="203"/>
-      <c r="G35" s="203"/>
-      <c r="H35" s="203"/>
-      <c r="I35" s="203"/>
-      <c r="J35" s="203"/>
-      <c r="K35" s="203"/>
-      <c r="L35" s="203"/>
-      <c r="M35" s="203"/>
-    </row>
-    <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="203"/>
-      <c r="C36" s="203"/>
-      <c r="D36" s="203"/>
-      <c r="E36" s="203"/>
-      <c r="F36" s="203"/>
-      <c r="G36" s="203"/>
-      <c r="H36" s="203"/>
-      <c r="I36" s="203"/>
-      <c r="J36" s="203"/>
-      <c r="K36" s="203"/>
-      <c r="L36" s="203"/>
-      <c r="M36" s="203"/>
-    </row>
-    <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="203"/>
-      <c r="C37" s="203"/>
-      <c r="D37" s="203"/>
-      <c r="E37" s="203"/>
-      <c r="F37" s="203"/>
-      <c r="G37" s="203"/>
-      <c r="H37" s="203"/>
-      <c r="I37" s="203"/>
-      <c r="J37" s="203"/>
-      <c r="K37" s="203"/>
-      <c r="L37" s="203"/>
-      <c r="M37" s="203"/>
+      <c r="C32" s="195"/>
+      <c r="D32" s="195"/>
+      <c r="E32" s="195"/>
+      <c r="F32" s="195"/>
+      <c r="G32" s="195"/>
+      <c r="H32" s="195"/>
+      <c r="I32" s="195"/>
+      <c r="J32" s="195"/>
+      <c r="K32" s="195"/>
+      <c r="L32" s="195"/>
+    </row>
+    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="195"/>
+      <c r="C33" s="195"/>
+      <c r="D33" s="195"/>
+      <c r="E33" s="195"/>
+      <c r="F33" s="195"/>
+      <c r="G33" s="195"/>
+      <c r="H33" s="195"/>
+      <c r="I33" s="195"/>
+      <c r="J33" s="195"/>
+      <c r="K33" s="195"/>
+      <c r="L33" s="195"/>
+    </row>
+    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="195"/>
+      <c r="C34" s="195"/>
+      <c r="D34" s="195"/>
+      <c r="E34" s="195"/>
+      <c r="F34" s="195"/>
+      <c r="G34" s="195"/>
+      <c r="H34" s="195"/>
+      <c r="I34" s="195"/>
+      <c r="J34" s="195"/>
+      <c r="K34" s="195"/>
+      <c r="L34" s="195"/>
+    </row>
+    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="195"/>
+      <c r="C35" s="195"/>
+      <c r="D35" s="195"/>
+      <c r="E35" s="195"/>
+      <c r="F35" s="195"/>
+      <c r="G35" s="195"/>
+      <c r="H35" s="195"/>
+      <c r="I35" s="195"/>
+      <c r="J35" s="195"/>
+      <c r="K35" s="195"/>
+      <c r="L35" s="195"/>
+    </row>
+    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="195"/>
+      <c r="C36" s="195"/>
+      <c r="D36" s="195"/>
+      <c r="E36" s="195"/>
+      <c r="F36" s="195"/>
+      <c r="G36" s="195"/>
+      <c r="H36" s="195"/>
+      <c r="I36" s="195"/>
+      <c r="J36" s="195"/>
+      <c r="K36" s="195"/>
+      <c r="L36" s="195"/>
+    </row>
+    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="195"/>
+      <c r="C37" s="195"/>
+      <c r="D37" s="195"/>
+      <c r="E37" s="195"/>
+      <c r="F37" s="195"/>
+      <c r="G37" s="195"/>
+      <c r="H37" s="195"/>
+      <c r="I37" s="195"/>
+      <c r="J37" s="195"/>
+      <c r="K37" s="195"/>
+      <c r="L37" s="195"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="B32:M37"/>
+  <mergeCells count="15">
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="B32:L37"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="G4:G5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D1:M1"/>
+    <mergeCell ref="D1:L1"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="H4:H5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4423,14 +4261,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="C5:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C5" s="190" t="s">
-        <v>98</v>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C5" s="185" t="s">
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
